--- a/Design Files/Oil-Diffuser-A-v1.0.0/BOM/eSpark-BOM-Oil-Diffuser-A-v1.0.0.xlsx
+++ b/Design Files/Oil-Diffuser-A-v1.0.0/BOM/eSpark-BOM-Oil-Diffuser-A-v1.0.0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="1 Boards" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="204">
   <si>
     <t>Component list</t>
   </si>
@@ -621,6 +621,18 @@
   </si>
   <si>
     <t>------</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Gardner Bender GSW-18 Heavy-Duty Electrical Toggle Switch, SPST, ON-OFF, 8 A/125 V, 6 inch Wire Terminal,Silver - ⅓ HP/125 V AC, 10 A/125 V AC</t>
+  </si>
+  <si>
+    <t>Toggle Switch</t>
   </si>
 </sst>
 </file>
@@ -1095,17 +1107,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1135,6 +1136,17 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1637,7 +1649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -1652,7 +1664,7 @@
     <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" customWidth="1"/>
     <col min="15" max="15" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="8.5703125" bestFit="1" customWidth="1"/>
@@ -1669,13 +1681,13 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
     </row>
     <row r="2" spans="1:17" ht="32.25" thickBot="1">
       <c r="A2" s="1"/>
@@ -1855,7 +1867,7 @@
       <c r="H8" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="I8" s="53" t="s">
+      <c r="I8" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J8" s="14" t="s">
@@ -1870,7 +1882,7 @@
       <c r="M8" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="N8" s="49" t="s">
+      <c r="N8" s="46" t="s">
         <v>174</v>
       </c>
       <c r="O8" s="21" t="s">
@@ -1906,7 +1918,7 @@
       <c r="H9" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="I9" s="53" t="s">
+      <c r="I9" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J9" s="20" t="s">
@@ -1921,7 +1933,7 @@
       <c r="M9" s="14">
         <v>2</v>
       </c>
-      <c r="N9" s="49" t="s">
+      <c r="N9" s="46" t="s">
         <v>174</v>
       </c>
       <c r="O9" s="21" t="s">
@@ -1957,7 +1969,7 @@
       <c r="H10" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="I10" s="53" t="s">
+      <c r="I10" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J10" s="14" t="s">
@@ -1972,7 +1984,7 @@
       <c r="M10" s="14">
         <v>2</v>
       </c>
-      <c r="N10" s="51" t="s">
+      <c r="N10" s="48" t="s">
         <v>174</v>
       </c>
       <c r="O10" s="21" t="s">
@@ -2008,7 +2020,7 @@
       <c r="H11" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="I11" s="53" t="s">
+      <c r="I11" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J11" s="20" t="s">
@@ -2023,7 +2035,7 @@
       <c r="M11" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="N11" s="51" t="s">
+      <c r="N11" s="48" t="s">
         <v>174</v>
       </c>
       <c r="O11" s="21" t="s">
@@ -2059,7 +2071,7 @@
       <c r="H12" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="I12" s="53" t="s">
+      <c r="I12" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J12" s="14" t="s">
@@ -2074,7 +2086,7 @@
       <c r="M12" s="14">
         <v>2</v>
       </c>
-      <c r="N12" s="49" t="s">
+      <c r="N12" s="46" t="s">
         <v>174</v>
       </c>
       <c r="O12" s="21" t="s">
@@ -2110,7 +2122,7 @@
       <c r="H13" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="I13" s="53" t="s">
+      <c r="I13" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J13" s="20" t="s">
@@ -2125,7 +2137,7 @@
       <c r="M13" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="N13" s="49" t="s">
+      <c r="N13" s="46" t="s">
         <v>174</v>
       </c>
       <c r="O13" s="21" t="s">
@@ -2161,7 +2173,7 @@
       <c r="H14" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="I14" s="53" t="s">
+      <c r="I14" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J14" s="14" t="s">
@@ -2176,7 +2188,7 @@
       <c r="M14" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="N14" s="49" t="s">
+      <c r="N14" s="46" t="s">
         <v>174</v>
       </c>
       <c r="O14" s="21" t="s">
@@ -2212,7 +2224,7 @@
       <c r="H15" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="I15" s="53" t="s">
+      <c r="I15" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J15" s="20" t="s">
@@ -2227,7 +2239,7 @@
       <c r="M15" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="N15" s="51" t="s">
+      <c r="N15" s="48" t="s">
         <v>174</v>
       </c>
       <c r="O15" s="21" t="s">
@@ -2263,7 +2275,7 @@
       <c r="H16" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="I16" s="53" t="s">
+      <c r="I16" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J16" s="14" t="s">
@@ -2278,7 +2290,7 @@
       <c r="M16" s="14">
         <v>2</v>
       </c>
-      <c r="N16" s="49" t="s">
+      <c r="N16" s="46" t="s">
         <v>174</v>
       </c>
       <c r="O16" s="21" t="s">
@@ -2314,7 +2326,7 @@
       <c r="H17" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="I17" s="53" t="s">
+      <c r="I17" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J17" s="20" t="s">
@@ -2329,7 +2341,7 @@
       <c r="M17" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="N17" s="51" t="s">
+      <c r="N17" s="48" t="s">
         <v>174</v>
       </c>
       <c r="O17" s="21" t="s">
@@ -2365,7 +2377,7 @@
       <c r="H18" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="I18" s="53" t="s">
+      <c r="I18" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J18" s="14" t="s">
@@ -2380,7 +2392,7 @@
       <c r="M18" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="N18" s="51" t="s">
+      <c r="N18" s="48" t="s">
         <v>174</v>
       </c>
       <c r="O18" s="21" t="s">
@@ -2416,7 +2428,7 @@
       <c r="H19" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="I19" s="53" t="s">
+      <c r="I19" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J19" s="20" t="s">
@@ -2431,7 +2443,7 @@
       <c r="M19" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="N19" s="51" t="s">
+      <c r="N19" s="48" t="s">
         <v>174</v>
       </c>
       <c r="O19" s="21" t="s">
@@ -2467,7 +2479,7 @@
       <c r="H20" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="I20" s="53" t="s">
+      <c r="I20" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J20" s="14" t="s">
@@ -2482,7 +2494,7 @@
       <c r="M20" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="N20" s="51" t="s">
+      <c r="N20" s="48" t="s">
         <v>174</v>
       </c>
       <c r="O20" s="21" t="s">
@@ -2518,7 +2530,7 @@
       <c r="H21" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="I21" s="53" t="s">
+      <c r="I21" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J21" s="20" t="s">
@@ -2533,7 +2545,7 @@
       <c r="M21" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="N21" s="51" t="s">
+      <c r="N21" s="48" t="s">
         <v>174</v>
       </c>
       <c r="O21" s="21" t="s">
@@ -2554,46 +2566,46 @@
       <c r="C22" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="50" t="s">
+      <c r="D22" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="50" t="s">
+      <c r="E22" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="50" t="s">
+      <c r="F22" s="47" t="s">
         <v>198</v>
       </c>
-      <c r="G22" s="50" t="s">
+      <c r="G22" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="H22" s="50" t="s">
+      <c r="H22" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="I22" s="54" t="s">
+      <c r="I22" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="J22" s="50" t="s">
+      <c r="J22" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="K22" s="50" t="s">
+      <c r="K22" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="L22" s="50">
+      <c r="L22" s="47">
         <v>2</v>
       </c>
-      <c r="M22" s="50">
+      <c r="M22" s="47">
         <v>6</v>
       </c>
-      <c r="N22" s="50" t="s">
+      <c r="N22" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="O22" s="50" t="s">
+      <c r="O22" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="P22" s="50" t="s">
+      <c r="P22" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="Q22" s="48" t="s">
+      <c r="Q22" s="45" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2621,7 +2633,7 @@
       <c r="H23" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="I23" s="53" t="s">
+      <c r="I23" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J23" s="20" t="s">
@@ -2636,7 +2648,7 @@
       <c r="M23" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="N23" s="51" t="s">
+      <c r="N23" s="48" t="s">
         <v>174</v>
       </c>
       <c r="O23" s="21" t="s">
@@ -2672,7 +2684,7 @@
       <c r="H24" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="I24" s="53" t="s">
+      <c r="I24" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J24" s="14" t="s">
@@ -2687,7 +2699,7 @@
       <c r="M24" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="N24" s="51" t="s">
+      <c r="N24" s="48" t="s">
         <v>174</v>
       </c>
       <c r="O24" s="21" t="s">
@@ -2723,7 +2735,7 @@
       <c r="H25" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="I25" s="53" t="s">
+      <c r="I25" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J25" s="20" t="s">
@@ -2738,7 +2750,7 @@
       <c r="M25" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="N25" s="51" t="s">
+      <c r="N25" s="48" t="s">
         <v>174</v>
       </c>
       <c r="O25" s="21" t="s">
@@ -2774,7 +2786,7 @@
       <c r="H26" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="I26" s="53" t="s">
+      <c r="I26" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J26" s="14" t="s">
@@ -2789,7 +2801,7 @@
       <c r="M26" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="N26" s="51" t="s">
+      <c r="N26" s="48" t="s">
         <v>174</v>
       </c>
       <c r="O26" s="21" t="s">
@@ -2810,46 +2822,46 @@
       <c r="C27" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="45" t="s">
+      <c r="D27" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="45" t="s">
+      <c r="E27" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="F27" s="50" t="s">
+      <c r="F27" s="47" t="s">
         <v>198</v>
       </c>
-      <c r="G27" s="45" t="s">
+      <c r="G27" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="H27" s="45" t="s">
+      <c r="H27" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="I27" s="53" t="s">
+      <c r="I27" s="50" t="s">
         <v>199</v>
       </c>
-      <c r="J27" s="45" t="s">
+      <c r="J27" s="42" t="s">
         <v>141</v>
       </c>
-      <c r="K27" s="45" t="s">
+      <c r="K27" s="42" t="s">
         <v>153</v>
       </c>
-      <c r="L27" s="45">
-        <v>1</v>
-      </c>
-      <c r="M27" s="46" t="s">
+      <c r="L27" s="42">
+        <v>1</v>
+      </c>
+      <c r="M27" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="N27" s="52" t="s">
+      <c r="N27" s="49" t="s">
         <v>166</v>
       </c>
-      <c r="O27" s="47" t="s">
+      <c r="O27" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="P27" s="47" t="s">
+      <c r="P27" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="Q27" s="48" t="s">
+      <c r="Q27" s="45" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2877,7 +2889,7 @@
       <c r="H28" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="I28" s="53" t="s">
+      <c r="I28" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J28" s="14" t="s">
@@ -2892,7 +2904,7 @@
       <c r="M28" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="N28" s="51" t="s">
+      <c r="N28" s="48" t="s">
         <v>174</v>
       </c>
       <c r="O28" s="21" t="s">
@@ -2928,7 +2940,7 @@
       <c r="H29" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="I29" s="53" t="s">
+      <c r="I29" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J29" s="20" t="s">
@@ -2943,7 +2955,7 @@
       <c r="M29" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="N29" s="51" t="s">
+      <c r="N29" s="48" t="s">
         <v>174</v>
       </c>
       <c r="O29" s="21" t="s">
@@ -2955,7 +2967,7 @@
       </c>
       <c r="Q29" s="20"/>
     </row>
-    <row r="30" spans="1:17" ht="15.75" thickBot="1">
+    <row r="30" spans="1:17">
       <c r="A30" s="1"/>
       <c r="B30" s="16">
         <f>ROW(B30) - ROW($B$7)</f>
@@ -2979,7 +2991,7 @@
       <c r="H30" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="I30" s="53" t="s">
+      <c r="I30" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J30" s="14" t="s">
@@ -2994,7 +3006,7 @@
       <c r="M30" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="N30" s="51" t="s">
+      <c r="N30" s="48" t="s">
         <v>174</v>
       </c>
       <c r="O30" s="21" t="s">
@@ -3006,34 +3018,77 @@
       </c>
       <c r="Q30" s="14"/>
     </row>
-    <row r="31" spans="1:17" ht="19.5" thickBot="1">
+    <row r="31" spans="1:17" ht="60.75" thickBot="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="43" t="s">
+      <c r="B31" s="16">
+        <f>ROW(B31) - ROW($B$7)</f>
+        <v>24</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="I31" s="50"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="14">
+        <v>1</v>
+      </c>
+      <c r="M31" s="14">
+        <v>1</v>
+      </c>
+      <c r="N31" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="O31" s="21">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="P31" s="15">
+        <f>O31*M31</f>
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="Q31" s="14"/>
+    </row>
+    <row r="32" spans="1:17" ht="19.5" thickBot="1">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="N31" s="44"/>
-      <c r="O31" s="44"/>
-      <c r="P31" s="18">
-        <f>SUM(P8:P30)</f>
-        <v>11.817299999999998</v>
-      </c>
-      <c r="Q31" s="1"/>
+      <c r="N32" s="54"/>
+      <c r="O32" s="54"/>
+      <c r="P32" s="18">
+        <f>SUM(P8:P31)</f>
+        <v>20.787299999999998</v>
+      </c>
+      <c r="Q32" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="M31:O31"/>
+    <mergeCell ref="M32:O32"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="N30" r:id="rId1"/>
@@ -3058,15 +3113,17 @@
     <hyperlink ref="N10" r:id="rId20"/>
     <hyperlink ref="N9" r:id="rId21"/>
     <hyperlink ref="N8" r:id="rId22"/>
+    <hyperlink ref="N31" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId24"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R44"/>
+  <dimension ref="A1:R45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="10" customWidth="1"/>
@@ -3099,14 +3156,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1">
       <c r="A2" s="1"/>
@@ -3294,7 +3351,7 @@
       <c r="H8" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="I8" s="53" t="s">
+      <c r="I8" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J8" s="14" t="s">
@@ -3313,7 +3370,7 @@
       <c r="N8" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="O8" s="49" t="s">
+      <c r="O8" s="46" t="s">
         <v>174</v>
       </c>
       <c r="P8" s="21" t="s">
@@ -3349,7 +3406,7 @@
       <c r="H9" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="I9" s="53" t="s">
+      <c r="I9" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J9" s="20" t="s">
@@ -3362,13 +3419,13 @@
         <v>1</v>
       </c>
       <c r="M9" s="14">
-        <f t="shared" ref="M9:M30" si="1">L9*3</f>
+        <f t="shared" ref="M9:M31" si="1">L9*3</f>
         <v>3</v>
       </c>
       <c r="N9" s="14">
         <v>4</v>
       </c>
-      <c r="O9" s="49" t="s">
+      <c r="O9" s="46" t="s">
         <v>174</v>
       </c>
       <c r="P9" s="21" t="s">
@@ -3404,7 +3461,7 @@
       <c r="H10" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="I10" s="53" t="s">
+      <c r="I10" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J10" s="14" t="s">
@@ -3423,7 +3480,7 @@
       <c r="N10" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="O10" s="51" t="s">
+      <c r="O10" s="48" t="s">
         <v>174</v>
       </c>
       <c r="P10" s="21" t="s">
@@ -3459,7 +3516,7 @@
       <c r="H11" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="I11" s="53" t="s">
+      <c r="I11" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J11" s="20" t="s">
@@ -3478,7 +3535,7 @@
       <c r="N11" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="O11" s="51" t="s">
+      <c r="O11" s="48" t="s">
         <v>174</v>
       </c>
       <c r="P11" s="21" t="s">
@@ -3514,7 +3571,7 @@
       <c r="H12" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="I12" s="53" t="s">
+      <c r="I12" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J12" s="14" t="s">
@@ -3533,7 +3590,7 @@
       <c r="N12" s="14">
         <v>4</v>
       </c>
-      <c r="O12" s="49" t="s">
+      <c r="O12" s="46" t="s">
         <v>174</v>
       </c>
       <c r="P12" s="21" t="s">
@@ -3569,7 +3626,7 @@
       <c r="H13" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="I13" s="53" t="s">
+      <c r="I13" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J13" s="20" t="s">
@@ -3588,7 +3645,7 @@
       <c r="N13" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="O13" s="49" t="s">
+      <c r="O13" s="46" t="s">
         <v>174</v>
       </c>
       <c r="P13" s="21" t="s">
@@ -3624,7 +3681,7 @@
       <c r="H14" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="I14" s="53" t="s">
+      <c r="I14" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J14" s="14" t="s">
@@ -3643,7 +3700,7 @@
       <c r="N14" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="O14" s="49" t="s">
+      <c r="O14" s="46" t="s">
         <v>174</v>
       </c>
       <c r="P14" s="21" t="s">
@@ -3679,7 +3736,7 @@
       <c r="H15" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="I15" s="53" t="s">
+      <c r="I15" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J15" s="20" t="s">
@@ -3698,7 +3755,7 @@
       <c r="N15" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="O15" s="51" t="s">
+      <c r="O15" s="48" t="s">
         <v>174</v>
       </c>
       <c r="P15" s="21" t="s">
@@ -3734,7 +3791,7 @@
       <c r="H16" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="I16" s="53" t="s">
+      <c r="I16" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J16" s="14" t="s">
@@ -3753,7 +3810,7 @@
       <c r="N16" s="14">
         <v>4</v>
       </c>
-      <c r="O16" s="49" t="s">
+      <c r="O16" s="46" t="s">
         <v>174</v>
       </c>
       <c r="P16" s="21" t="s">
@@ -3789,7 +3846,7 @@
       <c r="H17" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="I17" s="53" t="s">
+      <c r="I17" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J17" s="20" t="s">
@@ -3808,7 +3865,7 @@
       <c r="N17" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="O17" s="51" t="s">
+      <c r="O17" s="48" t="s">
         <v>174</v>
       </c>
       <c r="P17" s="21" t="s">
@@ -3844,7 +3901,7 @@
       <c r="H18" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="I18" s="53" t="s">
+      <c r="I18" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J18" s="14" t="s">
@@ -3863,7 +3920,7 @@
       <c r="N18" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="O18" s="51" t="s">
+      <c r="O18" s="48" t="s">
         <v>174</v>
       </c>
       <c r="P18" s="21" t="s">
@@ -3899,7 +3956,7 @@
       <c r="H19" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="I19" s="53" t="s">
+      <c r="I19" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J19" s="20" t="s">
@@ -3918,7 +3975,7 @@
       <c r="N19" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="O19" s="51" t="s">
+      <c r="O19" s="48" t="s">
         <v>174</v>
       </c>
       <c r="P19" s="21" t="s">
@@ -3954,7 +4011,7 @@
       <c r="H20" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="I20" s="53" t="s">
+      <c r="I20" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J20" s="14" t="s">
@@ -3973,7 +4030,7 @@
       <c r="N20" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="O20" s="51" t="s">
+      <c r="O20" s="48" t="s">
         <v>174</v>
       </c>
       <c r="P20" s="21" t="s">
@@ -4009,7 +4066,7 @@
       <c r="H21" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="I21" s="53" t="s">
+      <c r="I21" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J21" s="20" t="s">
@@ -4028,7 +4085,7 @@
       <c r="N21" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="O21" s="51" t="s">
+      <c r="O21" s="48" t="s">
         <v>174</v>
       </c>
       <c r="P21" s="21" t="s">
@@ -4049,50 +4106,50 @@
       <c r="C22" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="50" t="s">
+      <c r="D22" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="50" t="s">
+      <c r="E22" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="F22" s="50" t="s">
+      <c r="F22" s="47" t="s">
         <v>198</v>
       </c>
-      <c r="G22" s="50" t="s">
+      <c r="G22" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="H22" s="50" t="s">
+      <c r="H22" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="I22" s="54" t="s">
+      <c r="I22" s="51" t="s">
         <v>199</v>
       </c>
-      <c r="J22" s="50" t="s">
+      <c r="J22" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="K22" s="50" t="s">
+      <c r="K22" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="L22" s="50">
+      <c r="L22" s="47">
         <v>2</v>
       </c>
-      <c r="M22" s="50">
+      <c r="M22" s="47">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N22" s="50">
+      <c r="N22" s="47">
         <v>6</v>
       </c>
-      <c r="O22" s="50" t="s">
+      <c r="O22" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="P22" s="50" t="s">
+      <c r="P22" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="Q22" s="50" t="s">
+      <c r="Q22" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="R22" s="48" t="s">
+      <c r="R22" s="45" t="s">
         <v>167</v>
       </c>
     </row>
@@ -4120,7 +4177,7 @@
       <c r="H23" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="I23" s="53" t="s">
+      <c r="I23" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J23" s="20" t="s">
@@ -4139,7 +4196,7 @@
       <c r="N23" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="O23" s="51" t="s">
+      <c r="O23" s="48" t="s">
         <v>174</v>
       </c>
       <c r="P23" s="21" t="s">
@@ -4175,7 +4232,7 @@
       <c r="H24" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="I24" s="53" t="s">
+      <c r="I24" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J24" s="14" t="s">
@@ -4194,7 +4251,7 @@
       <c r="N24" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="O24" s="51" t="s">
+      <c r="O24" s="48" t="s">
         <v>174</v>
       </c>
       <c r="P24" s="21" t="s">
@@ -4230,7 +4287,7 @@
       <c r="H25" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="I25" s="53" t="s">
+      <c r="I25" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J25" s="20" t="s">
@@ -4249,7 +4306,7 @@
       <c r="N25" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="O25" s="51" t="s">
+      <c r="O25" s="48" t="s">
         <v>174</v>
       </c>
       <c r="P25" s="21" t="s">
@@ -4285,7 +4342,7 @@
       <c r="H26" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="I26" s="53" t="s">
+      <c r="I26" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J26" s="14" t="s">
@@ -4304,7 +4361,7 @@
       <c r="N26" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="O26" s="51" t="s">
+      <c r="O26" s="48" t="s">
         <v>174</v>
       </c>
       <c r="P26" s="21" t="s">
@@ -4325,50 +4382,50 @@
       <c r="C27" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="45" t="s">
+      <c r="D27" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="45" t="s">
+      <c r="E27" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="F27" s="50" t="s">
+      <c r="F27" s="47" t="s">
         <v>198</v>
       </c>
-      <c r="G27" s="45" t="s">
+      <c r="G27" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="H27" s="45" t="s">
+      <c r="H27" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="I27" s="53" t="s">
+      <c r="I27" s="50" t="s">
         <v>199</v>
       </c>
-      <c r="J27" s="45" t="s">
+      <c r="J27" s="42" t="s">
         <v>141</v>
       </c>
-      <c r="K27" s="45" t="s">
+      <c r="K27" s="42" t="s">
         <v>153</v>
       </c>
-      <c r="L27" s="45">
-        <v>1</v>
-      </c>
-      <c r="M27" s="46">
+      <c r="L27" s="42">
+        <v>1</v>
+      </c>
+      <c r="M27" s="43">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="N27" s="46" t="s">
+      <c r="N27" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="O27" s="52" t="s">
+      <c r="O27" s="49" t="s">
         <v>166</v>
       </c>
-      <c r="P27" s="47" t="s">
+      <c r="P27" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="Q27" s="47" t="s">
+      <c r="Q27" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="R27" s="48" t="s">
+      <c r="R27" s="45" t="s">
         <v>167</v>
       </c>
     </row>
@@ -4396,7 +4453,7 @@
       <c r="H28" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="I28" s="53" t="s">
+      <c r="I28" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J28" s="14" t="s">
@@ -4415,7 +4472,7 @@
       <c r="N28" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="O28" s="51" t="s">
+      <c r="O28" s="48" t="s">
         <v>174</v>
       </c>
       <c r="P28" s="21" t="s">
@@ -4451,7 +4508,7 @@
       <c r="H29" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="I29" s="53" t="s">
+      <c r="I29" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J29" s="20" t="s">
@@ -4470,7 +4527,7 @@
       <c r="N29" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="O29" s="51" t="s">
+      <c r="O29" s="48" t="s">
         <v>174</v>
       </c>
       <c r="P29" s="21" t="s">
@@ -4482,7 +4539,7 @@
       </c>
       <c r="R29" s="20"/>
     </row>
-    <row r="30" spans="1:18" ht="15.75" thickBot="1">
+    <row r="30" spans="1:18">
       <c r="A30" s="1"/>
       <c r="B30" s="16">
         <f>ROW(B30) - ROW($B$7)</f>
@@ -4506,7 +4563,7 @@
       <c r="H30" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="I30" s="53" t="s">
+      <c r="I30" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J30" s="14" t="s">
@@ -4525,7 +4582,7 @@
       <c r="N30" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="O30" s="51" t="s">
+      <c r="O30" s="48" t="s">
         <v>174</v>
       </c>
       <c r="P30" s="21" t="s">
@@ -4537,30 +4594,54 @@
       </c>
       <c r="R30" s="14"/>
     </row>
-    <row r="31" spans="1:18" ht="19.5" thickBot="1">
+    <row r="31" spans="1:18" ht="60.75" thickBot="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="43" t="s">
+      <c r="B31" s="16">
+        <f>ROW(B31) - ROW($B$7)</f>
+        <v>24</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="I31" s="50"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="14">
+        <v>1</v>
+      </c>
+      <c r="M31" s="14">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="O31" s="44"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="18">
-        <f>SUM(Q8:Q30)</f>
-        <v>15.214600000000001</v>
-      </c>
-      <c r="R31" s="1"/>
+      <c r="N31" s="14">
+        <v>3</v>
+      </c>
+      <c r="O31" s="48" t="s">
+        <v>201</v>
+      </c>
+      <c r="P31" s="21">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="Q31" s="15">
+        <f>P31*M31</f>
+        <v>26.910000000000004</v>
+      </c>
+      <c r="R31" s="15" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="32" spans="1:18" ht="19.5" thickBot="1">
       <c r="A32" s="1"/>
@@ -4576,25 +4657,48 @@
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
-      <c r="N32" s="43" t="s">
+      <c r="N32" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="54"/>
+      <c r="P32" s="54"/>
+      <c r="Q32" s="18">
+        <f>SUM(Q8:Q31)</f>
+        <v>42.124600000000001</v>
+      </c>
+      <c r="R32" s="1"/>
+    </row>
+    <row r="33" spans="2:17" ht="19.5" thickBot="1">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="O32" s="44"/>
-      <c r="P32" s="44"/>
-      <c r="Q32" s="19">
-        <f>Q31/3</f>
-        <v>5.0715333333333339</v>
-      </c>
-      <c r="R32" s="1"/>
-    </row>
-    <row r="44" spans="13:13">
-      <c r="M44" s="38"/>
+      <c r="O33" s="54"/>
+      <c r="P33" s="54"/>
+      <c r="Q33" s="19">
+        <f>Q32/3</f>
+        <v>14.041533333333334</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17">
+      <c r="M45" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N31:P31"/>
     <mergeCell ref="N32:P32"/>
+    <mergeCell ref="N33:P33"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O8" r:id="rId1"/>
@@ -4619,8 +4723,9 @@
     <hyperlink ref="O28" r:id="rId20"/>
     <hyperlink ref="O29" r:id="rId21"/>
     <hyperlink ref="O30" r:id="rId22"/>
+    <hyperlink ref="O31" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId23"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
 </worksheet>
 </file>
--- a/Design Files/Oil-Diffuser-A-v1.0.0/BOM/eSpark-BOM-Oil-Diffuser-A-v1.0.0.xlsx
+++ b/Design Files/Oil-Diffuser-A-v1.0.0/BOM/eSpark-BOM-Oil-Diffuser-A-v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="208">
   <si>
     <t>Component list</t>
   </si>
@@ -626,13 +626,25 @@
     <t>Peripheral</t>
   </si>
   <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t>Gardner Bender GSW-18 Heavy-Duty Electrical Toggle Switch, SPST, ON-OFF, 8 A/125 V, 6 inch Wire Terminal,Silver - ⅓ HP/125 V AC, 10 A/125 V AC</t>
-  </si>
-  <si>
     <t>Toggle Switch</t>
+  </si>
+  <si>
+    <t>AC 250V 6A On/Off Prewired Standard Toggle Switch With Wire Cable KNS-1 SPST Contacts Switch Electrical Equipment</t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>1Pcs Gdstime DC 5V 12V 24V 75mm x 30mm Centrifugal Blower Fan 7530 7.5cm Dual Ball Turbo Radiator Fan 75mm Purifier Heatsink Fan</t>
+  </si>
+  <si>
+    <t>Blower Fan</t>
+  </si>
+  <si>
+    <t>Charger</t>
+  </si>
+  <si>
+    <t>24V0.5A New AC 100V-240V Converter Switching Power Adapter DC 24V 0.5A 500mA Universla Power Supply EU Plug Tablet Charger</t>
   </si>
 </sst>
 </file>
@@ -1649,7 +1661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -3018,7 +3030,7 @@
       </c>
       <c r="Q30" s="14"/>
     </row>
-    <row r="31" spans="1:17" ht="60.75" thickBot="1">
+    <row r="31" spans="1:17" ht="48">
       <c r="A31" s="1"/>
       <c r="B31" s="16">
         <f>ROW(B31) - ROW($B$7)</f>
@@ -3033,62 +3045,172 @@
       <c r="E31" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="F31" s="14"/>
+      <c r="F31" s="14" t="s">
+        <v>166</v>
+      </c>
       <c r="G31" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="I31" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="L31" s="14">
+        <v>1</v>
+      </c>
+      <c r="M31" s="14">
+        <v>1</v>
+      </c>
+      <c r="N31" s="48" t="s">
         <v>203</v>
       </c>
-      <c r="H31" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="I31" s="50"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="14">
-        <v>1</v>
-      </c>
-      <c r="M31" s="14">
-        <v>1</v>
-      </c>
-      <c r="N31" s="48" t="s">
-        <v>201</v>
-      </c>
       <c r="O31" s="21">
-        <v>8.9700000000000006</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P31" s="15">
         <f>O31*M31</f>
-        <v>8.9700000000000006</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="Q31" s="14"/>
     </row>
-    <row r="32" spans="1:17" ht="19.5" thickBot="1">
+    <row r="32" spans="1:17" ht="60">
       <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="53" t="s">
+      <c r="B32" s="16">
+        <f t="shared" ref="B32:B33" si="11">ROW(B32) - ROW($B$7)</f>
+        <v>25</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="I32" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="L32" s="14">
+        <v>1</v>
+      </c>
+      <c r="M32" s="14">
+        <v>1</v>
+      </c>
+      <c r="N32" s="48" t="s">
+        <v>203</v>
+      </c>
+      <c r="O32" s="21">
+        <v>13.58</v>
+      </c>
+      <c r="P32" s="15">
+        <f>O32*M32</f>
+        <v>13.58</v>
+      </c>
+      <c r="Q32" s="14"/>
+    </row>
+    <row r="33" spans="1:17" ht="60.75" thickBot="1">
+      <c r="A33" s="1"/>
+      <c r="B33" s="16">
+        <f t="shared" si="11"/>
+        <v>26</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="I33" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="K33" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="L33" s="14">
+        <v>1</v>
+      </c>
+      <c r="M33" s="14">
+        <v>1</v>
+      </c>
+      <c r="N33" s="48" t="s">
+        <v>203</v>
+      </c>
+      <c r="O33" s="21">
         <v>3</v>
       </c>
-      <c r="N32" s="54"/>
-      <c r="O32" s="54"/>
-      <c r="P32" s="18">
-        <f>SUM(P8:P31)</f>
-        <v>20.787299999999998</v>
-      </c>
-      <c r="Q32" s="1"/>
+      <c r="P33" s="15">
+        <f>O33*M33</f>
+        <v>3</v>
+      </c>
+      <c r="Q33" s="14"/>
+    </row>
+    <row r="34" spans="1:17" ht="19.5" thickBot="1">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="N34" s="54"/>
+      <c r="O34" s="54"/>
+      <c r="P34" s="18">
+        <f>SUM(P8:P33)</f>
+        <v>29.5473</v>
+      </c>
+      <c r="Q34" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="M34:O34"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="N30" r:id="rId1"/>
@@ -3114,16 +3236,18 @@
     <hyperlink ref="N9" r:id="rId21"/>
     <hyperlink ref="N8" r:id="rId22"/>
     <hyperlink ref="N31" r:id="rId23"/>
+    <hyperlink ref="N32" r:id="rId24"/>
+    <hyperlink ref="N33" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId24"/>
+  <pageSetup orientation="portrait" r:id="rId26"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="10" customWidth="1"/>
@@ -3419,7 +3543,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="14">
-        <f t="shared" ref="M9:M31" si="1">L9*3</f>
+        <f t="shared" ref="M9:M33" si="1">L9*3</f>
         <v>3</v>
       </c>
       <c r="N9" s="14">
@@ -4594,7 +4718,7 @@
       </c>
       <c r="R30" s="14"/>
     </row>
-    <row r="31" spans="1:18" ht="60.75" thickBot="1">
+    <row r="31" spans="1:18" ht="48">
       <c r="A31" s="1"/>
       <c r="B31" s="16">
         <f>ROW(B31) - ROW($B$7)</f>
@@ -4609,16 +4733,24 @@
       <c r="E31" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="F31" s="14"/>
+      <c r="F31" s="14" t="s">
+        <v>166</v>
+      </c>
       <c r="G31" s="14" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H31" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="I31" s="50"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="20"/>
+      <c r="I31" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="J31" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>166</v>
+      </c>
       <c r="L31" s="14">
         <v>1</v>
       </c>
@@ -4630,75 +4762,189 @@
         <v>3</v>
       </c>
       <c r="O31" s="48" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="P31" s="21">
-        <v>8.9700000000000006</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="Q31" s="15">
         <f>P31*M31</f>
-        <v>26.910000000000004</v>
+        <v>3.4499999999999997</v>
       </c>
       <c r="R31" s="15" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="19.5" thickBot="1">
+    <row r="32" spans="1:18" ht="48">
       <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="53" t="s">
+      <c r="B32" s="16">
+        <f t="shared" ref="B32:B33" si="12">ROW(B32) - ROW($B$7)</f>
+        <v>25</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="I32" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="J32" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="L32" s="14">
+        <v>1</v>
+      </c>
+      <c r="M32" s="14">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="O32" s="54"/>
-      <c r="P32" s="54"/>
-      <c r="Q32" s="18">
-        <f>SUM(Q8:Q31)</f>
-        <v>42.124600000000001</v>
-      </c>
-      <c r="R32" s="1"/>
-    </row>
-    <row r="33" spans="2:17" ht="19.5" thickBot="1">
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="53" t="s">
+      <c r="N32" s="14">
+        <v>3</v>
+      </c>
+      <c r="O32" s="48" t="s">
+        <v>203</v>
+      </c>
+      <c r="P32" s="21">
+        <v>13.58</v>
+      </c>
+      <c r="Q32" s="15">
+        <f t="shared" ref="Q32:Q33" si="13">P32*M32</f>
+        <v>40.74</v>
+      </c>
+      <c r="R32" s="15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="48.75" thickBot="1">
+      <c r="A33" s="1"/>
+      <c r="B33" s="16">
+        <f t="shared" si="12"/>
+        <v>26</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="I33" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="K33" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="L33" s="14">
+        <v>1</v>
+      </c>
+      <c r="M33" s="14">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N33" s="14">
+        <v>3</v>
+      </c>
+      <c r="O33" s="48" t="s">
+        <v>203</v>
+      </c>
+      <c r="P33" s="21">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="15">
+        <f t="shared" si="13"/>
+        <v>9</v>
+      </c>
+      <c r="R33" s="15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="19.5" thickBot="1">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="O34" s="54"/>
+      <c r="P34" s="54"/>
+      <c r="Q34" s="18">
+        <f>SUM(Q8:Q33)</f>
+        <v>68.404600000000002</v>
+      </c>
+      <c r="R34" s="1"/>
+    </row>
+    <row r="35" spans="1:18" ht="19.5" thickBot="1">
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="O33" s="54"/>
-      <c r="P33" s="54"/>
-      <c r="Q33" s="19">
-        <f>Q32/3</f>
-        <v>14.041533333333334</v>
-      </c>
-    </row>
-    <row r="45" spans="2:17">
-      <c r="M45" s="38"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="19">
+        <f>Q34/3</f>
+        <v>22.801533333333335</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
+      <c r="M47" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="N35:P35"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O8" r:id="rId1"/>
@@ -4724,8 +4970,10 @@
     <hyperlink ref="O29" r:id="rId21"/>
     <hyperlink ref="O30" r:id="rId22"/>
     <hyperlink ref="O31" r:id="rId23"/>
+    <hyperlink ref="O32" r:id="rId24"/>
+    <hyperlink ref="O33" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
 </worksheet>
 </file>
--- a/Design Files/Oil-Diffuser-A-v1.0.0/BOM/eSpark-BOM-Oil-Diffuser-A-v1.0.0.xlsx
+++ b/Design Files/Oil-Diffuser-A-v1.0.0/BOM/eSpark-BOM-Oil-Diffuser-A-v1.0.0.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="212">
   <si>
     <t>Component list</t>
   </si>
@@ -645,6 +645,18 @@
   </si>
   <si>
     <t>24V0.5A New AC 100V-240V Converter Switching Power Adapter DC 24V 0.5A 500mA Universla Power Supply EU Plug Tablet Charger</t>
+  </si>
+  <si>
+    <t>±10% 50V 100nF X7R Plugin,P=2.54mm Multilayer Ceramic Capacitors MLCC - Leaded ROHS</t>
+  </si>
+  <si>
+    <t>178MU0006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KNSCHA </t>
+  </si>
+  <si>
+    <t>C5632430</t>
   </si>
 </sst>
 </file>
@@ -1906,7 +1918,7 @@
       </c>
       <c r="Q8" s="14"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" ht="48">
       <c r="A9" s="1"/>
       <c r="B9" s="17">
         <f t="shared" ref="B9:B29" si="0">ROW(B9) - ROW($B$7)</f>
@@ -1919,22 +1931,22 @@
         <v>24</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>48</v>
+        <v>208</v>
       </c>
       <c r="F9" s="14" t="s">
         <v>198</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>72</v>
+        <v>209</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>106</v>
+        <v>210</v>
       </c>
       <c r="I9" s="50" t="s">
         <v>199</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="K9" s="20" t="s">
         <v>145</v>
@@ -1943,17 +1955,17 @@
         <v>1</v>
       </c>
       <c r="M9" s="14">
-        <v>2</v>
-      </c>
-      <c r="N9" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="N9" s="48" t="s">
         <v>174</v>
       </c>
-      <c r="O9" s="21" t="s">
-        <v>176</v>
+      <c r="O9" s="21">
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="P9" s="21">
         <f t="shared" ref="P9" si="1">O9*M9</f>
-        <v>1.2847999999999999</v>
+        <v>0.59500000000000008</v>
       </c>
       <c r="Q9" s="20"/>
     </row>
@@ -3203,7 +3215,7 @@
       <c r="O34" s="54"/>
       <c r="P34" s="18">
         <f>SUM(P8:P33)</f>
-        <v>29.5473</v>
+        <v>28.857500000000002</v>
       </c>
       <c r="Q34" s="1"/>
     </row>
@@ -3233,11 +3245,11 @@
     <hyperlink ref="N12" r:id="rId18"/>
     <hyperlink ref="N11" r:id="rId19"/>
     <hyperlink ref="N10" r:id="rId20"/>
-    <hyperlink ref="N9" r:id="rId21"/>
-    <hyperlink ref="N8" r:id="rId22"/>
-    <hyperlink ref="N31" r:id="rId23"/>
-    <hyperlink ref="N32" r:id="rId24"/>
-    <hyperlink ref="N33" r:id="rId25"/>
+    <hyperlink ref="N8" r:id="rId21"/>
+    <hyperlink ref="N31" r:id="rId22"/>
+    <hyperlink ref="N32" r:id="rId23"/>
+    <hyperlink ref="N33" r:id="rId24"/>
+    <hyperlink ref="N9" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId26"/>

--- a/Design Files/Oil-Diffuser-A-v1.0.0/BOM/eSpark-BOM-Oil-Diffuser-A-v1.0.0.xlsx
+++ b/Design Files/Oil-Diffuser-A-v1.0.0/BOM/eSpark-BOM-Oil-Diffuser-A-v1.0.0.xlsx
@@ -5,22 +5,22 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\elliotrosenberg-oildiffuser\Design Files\Oil-Diffuser-A-v1.0.0\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftikhar Ahmed\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="1 Boards" sheetId="2" r:id="rId1"/>
-    <sheet name="3 Boards" sheetId="1" r:id="rId2"/>
+    <sheet name="1 Board" sheetId="1" r:id="rId1"/>
+    <sheet name="3 Boards" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="309">
   <si>
     <t>Component list</t>
   </si>
@@ -40,12 +40,12 @@
     <t>Item Type</t>
   </si>
   <si>
+    <t>Capacitors</t>
+  </si>
+  <si>
     <t>Capacitor</t>
   </si>
   <si>
-    <t>Capacitors</t>
-  </si>
-  <si>
     <t>Diode</t>
   </si>
   <si>
@@ -55,25 +55,28 @@
     <t>Terminal Blocks</t>
   </si>
   <si>
+    <t>Wire To Board Connector</t>
+  </si>
+  <si>
     <t>DC Jack</t>
   </si>
   <si>
     <t>Right Angle JST</t>
   </si>
   <si>
-    <t>Wire To Board Connector</t>
-  </si>
-  <si>
     <t>Inductor</t>
   </si>
   <si>
     <t>LED</t>
   </si>
   <si>
-    <t>TEST POINT</t>
-  </si>
-  <si>
-    <t>MOSFET</t>
+    <t>Mosfet</t>
+  </si>
+  <si>
+    <t>BJTs</t>
+  </si>
+  <si>
+    <t>MOSFETs</t>
   </si>
   <si>
     <t>Resistor</t>
@@ -91,15 +94,18 @@
     <t>Designator</t>
   </si>
   <si>
-    <t>C1, C4</t>
-  </si>
-  <si>
-    <t>C2</t>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2, C9</t>
   </si>
   <si>
     <t>C3</t>
   </si>
   <si>
+    <t>C4</t>
+  </si>
+  <si>
     <t>C5</t>
   </si>
   <si>
@@ -109,7 +115,10 @@
     <t>C7</t>
   </si>
   <si>
-    <t>D1</t>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>D1, D2</t>
   </si>
   <si>
     <t>F1</t>
@@ -130,15 +139,24 @@
     <t>L1</t>
   </si>
   <si>
+    <t>L2</t>
+  </si>
+  <si>
     <t>LED1</t>
   </si>
   <si>
-    <t>P1, P2</t>
-  </si>
-  <si>
     <t>Q1</t>
   </si>
   <si>
+    <t>Q2, Q4</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>Q5</t>
+  </si>
+  <si>
     <t>R1</t>
   </si>
   <si>
@@ -148,31 +166,61 @@
     <t>R3</t>
   </si>
   <si>
-    <t>R4</t>
+    <t>R4, R10</t>
   </si>
   <si>
     <t>R5</t>
   </si>
   <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>R12, R14</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
     <t>U1</t>
   </si>
   <si>
     <t>U2</t>
   </si>
   <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
-    <t>CAP CER 0.1UF 100V X7R 0603</t>
-  </si>
-  <si>
-    <t>CAP CER 10000PF 1KV X7R RADIAL</t>
-  </si>
-  <si>
-    <t>100uF 80V 735mA@100kHz ±20% SMD,D8xL14.5mm Aluminum Electrolytic Capacitors - SMD ROHS</t>
-  </si>
-  <si>
-    <t>100nF ±5% 100V Plugin,P=5mm Polypropylene Film Capacitors (CBB) ROHS</t>
+    <t>470uF 35V 850mA@100KHz 80mΩ@100KHz ±20% SMD,D8xL10.5mm Aluminum Electrolytic Capacitors - SMD ROHS</t>
+  </si>
+  <si>
+    <t>1uF 25V X5R ±20% 0603 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+  </si>
+  <si>
+    <t>220uF 35V 600mA@100KHz 160mΩ@100KHz ±20% SMD,D6.3xL7.7mm Aluminum Electrolytic Capacitors - SMD ROHS</t>
+  </si>
+  <si>
+    <t>CAP CER 2.2UF 25V X5R 0603</t>
+  </si>
+  <si>
+    <t>5% 630V 47nF Plugin,P=5.08mm Film Capacitors ROHS</t>
   </si>
   <si>
     <t>CAP CER 100UF 16V X5R 1210</t>
@@ -181,80 +229,127 @@
     <t>CAP CER 10000PF 50V X8R 0603</t>
   </si>
   <si>
+    <t>±5% 50V 220pF NP0 Plugin,P=5.08mm Multilayer Ceramic Capacitors MLCC - Leaded ROHS</t>
+  </si>
+  <si>
     <t>SCHOTTKY DIODE SMB 100V 5A</t>
   </si>
   <si>
-    <t>50A SMD Fuse 1A 63V 63V 1206 Disposable fuses ROHS_x000D_
-PTC RESET FUSE 6V 3A 1206</t>
+    <t>33V 1.5A 40A 3A 1812 Resettable Fuses ROHS</t>
   </si>
   <si>
     <t>TERM BLK 2P SIDE ENT 5.08MM PCB</t>
   </si>
   <si>
+    <t>1x2P 2P XH 1 Tin 2.5mm 2 -25℃~+85℃ Brass 3A Straight Plugin,P=2.5mm Wire To Board Connector ROHS</t>
+  </si>
+  <si>
     <t>DC Power Receptacle 260℃ Brass -20℃~+70℃ 2.5mm 6mm 2.5A 24V Plugin AC/DC Power Connectors ROHS</t>
   </si>
   <si>
     <t>1x2P 1 2mm Male pin 2 -25℃~+85℃ 2A Surface Mount SMD,P=2mm Wire To Board / Wire To Wire Connector ROHS</t>
   </si>
   <si>
-    <t>1x2P 2P XH 1 Tin 2.5mm 2 -25℃~+85℃ Brass 3A Straight Plugin,P=2.5mm Wire To Board Connector ROHS</t>
-  </si>
-  <si>
-    <t>FIXED IND 220UH 500MA 1.495 OHM</t>
+    <t>2A 68uH ±20% 2.5A SMD,6.6x7.1mm Power Inductors ROHS</t>
+  </si>
+  <si>
+    <t>600mA 220uH EI-core Inductor ±20% Plugin Power Inductors ROHS</t>
   </si>
   <si>
     <t>White light 0603 Light Emitting Diodes (LED) ROHS</t>
   </si>
   <si>
-    <t>Test Point ON</t>
-  </si>
-  <si>
-    <t>MOSFET N-CH 55V 17A DPAK</t>
+    <t>30V 5.8A 32mΩ@10V,5.8A 1.4W 1.4V@250uA N Channel SOT-23 MOSFETs ROHS</t>
+  </si>
+  <si>
+    <t>TRANS NPN 40V 1A SOT23-3</t>
+  </si>
+  <si>
+    <t>100V 15A 96W 114mΩ@10V,3A 3.5V@250uA 1 N-Channel TO-252 MOSFETs ROHS</t>
+  </si>
+  <si>
+    <t>30V 7A 19mΩ 1.9W 1.1V@250uA P Channel SOT-23-3L MOSFETs ROHS</t>
   </si>
   <si>
     <t>RES 1K OHM 1% 1/8W 0805</t>
   </si>
   <si>
-    <t>RES 10 OHM 1% 1/4W 1206</t>
-  </si>
-  <si>
-    <t>RES SMD 100 OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>Cermet Not Linear VERTICAL Trimmer Potentiometer 卤10% 280deg 500mW 85C</t>
-  </si>
-  <si>
-    <t>RES 470 OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>IC REG LINEAR 12V 100MA SOT89-3</t>
-  </si>
-  <si>
-    <t>NO SOP-8 Timers ROHS</t>
+    <t>RES SMD 1M OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>Metal Film Resistors 1kΩ 250mW ±200ppm/℃ ±1% Plugin,D2.3xL6.5mm Through Hole Resistors ROHS</t>
+  </si>
+  <si>
+    <t>10% 5kΩ Plugin Potentiometers, Variable Resistors ROHS</t>
+  </si>
+  <si>
+    <t>RES 100K OHM 1% 1/8W 0805</t>
+  </si>
+  <si>
+    <t>RES 10 OHM 1% 3/4W 2010</t>
+  </si>
+  <si>
+    <t>RES 1K OHM 1% 1/2W 1206</t>
+  </si>
+  <si>
+    <t>Metal Film Resistors 1.5kΩ 250mW ±100ppm/℃ ±1% Plugin,D2.3xL6.5mm Through Hole Resistors ROHS</t>
+  </si>
+  <si>
+    <t>RES SMD 10K OHM 0.1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RES SMD 47OHM 0.1W 0603</t>
+  </si>
+  <si>
+    <t>RES 1.5K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RES SMD 270 OHM 0.1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>Step-down type Fixed 12V 2A 4.5V~40V ESOP-8 DC-DC Converters ROHS</t>
+  </si>
+  <si>
+    <t>IC BINARY COUNTER 14-BIT 16SOIC</t>
+  </si>
+  <si>
+    <t>IC OSC SINGLE TIMER 2.7MHZ 8SOIC</t>
+  </si>
+  <si>
+    <t>IC GATE DRVR IGBT/MOSFET SOT23-6</t>
   </si>
   <si>
     <t>Footprint</t>
   </si>
   <si>
+    <t>189RV0027</t>
+  </si>
+  <si>
     <t>Cap-0603</t>
   </si>
   <si>
-    <t>RDER73A103K2K1H03B</t>
-  </si>
-  <si>
-    <t>VKMD1451K101MV</t>
-  </si>
-  <si>
-    <t>MEM104J2A-7-50R0-T3.5</t>
+    <t>189RV0019</t>
+  </si>
+  <si>
+    <t>CAP-0603</t>
+  </si>
+  <si>
+    <t>CFA2J473JC4PK5136A00</t>
   </si>
   <si>
     <t>Cap-1210</t>
   </si>
   <si>
+    <t>CD1H221JC9BECHE100</t>
+  </si>
+  <si>
     <t>SMB_</t>
   </si>
   <si>
-    <t>Fuse 1206 (3216 Metric)</t>
+    <t>Fuse-1812_</t>
+  </si>
+  <si>
+    <t>XH-2A-L</t>
   </si>
   <si>
     <t>DC-0360-2.5</t>
@@ -263,40 +358,64 @@
     <t>WAFER-PH2.0-2PWB</t>
   </si>
   <si>
-    <t>XH-2A-L</t>
+    <t>PSPMAA0605H-680M-IGF</t>
+  </si>
+  <si>
+    <t>PK0810-221MB</t>
   </si>
   <si>
     <t>LED-0603</t>
   </si>
   <si>
-    <t>Test-point</t>
-  </si>
-  <si>
-    <t>DPAK</t>
+    <t>sot-23</t>
+  </si>
+  <si>
+    <t>SOT-23</t>
+  </si>
+  <si>
+    <t>TO-252-2L</t>
+  </si>
+  <si>
+    <t>SOT-23-3L_</t>
   </si>
   <si>
     <t>RES-0805</t>
   </si>
   <si>
+    <t>Res-0603</t>
+  </si>
+  <si>
+    <t>Plugin,D2.3xL6.5mm</t>
+  </si>
+  <si>
+    <t>3296W-1-502</t>
+  </si>
+  <si>
+    <t>RES-2010</t>
+  </si>
+  <si>
     <t>Res-1206</t>
   </si>
   <si>
-    <t>Res-0603</t>
-  </si>
-  <si>
-    <t>3386P-1-502LF</t>
-  </si>
-  <si>
-    <t>SOT-89-3</t>
-  </si>
-  <si>
-    <t>SOP-8</t>
+    <t>ESOP-8</t>
+  </si>
+  <si>
+    <t>16-SOIC (0.154", 3.90mm Width)</t>
+  </si>
+  <si>
+    <t>SOIC-8(0.154", 3.90mm Width)</t>
+  </si>
+  <si>
+    <t>SOT-23-6</t>
   </si>
   <si>
     <t>Manufacturer Part Number</t>
   </si>
   <si>
-    <t>CC0603KRX7R0BB104</t>
+    <t>TCC0603X5R105M250CT</t>
+  </si>
+  <si>
+    <t>CC0603KRX5R8BB225</t>
   </si>
   <si>
     <t>EMK325ABJ107MM-P</t>
@@ -305,211 +424,364 @@
     <t>SS510B</t>
   </si>
   <si>
-    <t>JFC1206-1100FS</t>
-  </si>
-  <si>
-    <t>VLS6045EX-221M</t>
+    <t>BSMD1812-150-33V</t>
   </si>
   <si>
     <t>NCD0603W3</t>
   </si>
   <si>
-    <t>IRFR024NTRPBF</t>
+    <t>AO3400A</t>
+  </si>
+  <si>
+    <t>ZXTN2040FTA</t>
+  </si>
+  <si>
+    <t>STD12N10L-VB</t>
+  </si>
+  <si>
+    <t>G7P03L</t>
   </si>
   <si>
     <t>RC0805FR-071KL</t>
   </si>
   <si>
-    <t>RC1206FR-0710RL</t>
-  </si>
-  <si>
-    <t>CRCW0603100RFKEA</t>
-  </si>
-  <si>
-    <t>RC0603FR-07470RL</t>
-  </si>
-  <si>
-    <t>L78L12ABUTR</t>
-  </si>
-  <si>
-    <t>NE555DTR(XBLW)</t>
+    <t>CRCW06031M00FKEA</t>
+  </si>
+  <si>
+    <t>MF1/4W-1KΩ±1%T52</t>
+  </si>
+  <si>
+    <t>RC0805FR-07100KL</t>
+  </si>
+  <si>
+    <t>RC2010FK-0710RL</t>
+  </si>
+  <si>
+    <t>RC1206FR-7W1KL</t>
+  </si>
+  <si>
+    <t>MF1/4W-1.5KΩ±1% T</t>
+  </si>
+  <si>
+    <t>RT0603BRD0710KL</t>
+  </si>
+  <si>
+    <t>RC0603FR-0747RL</t>
+  </si>
+  <si>
+    <t>RC0603FR-071K5L</t>
+  </si>
+  <si>
+    <t>RT0603BRE07270RL</t>
+  </si>
+  <si>
+    <t>XL1509E-12</t>
+  </si>
+  <si>
+    <t>CD4060BM96</t>
+  </si>
+  <si>
+    <t>TS555IDTTR</t>
+  </si>
+  <si>
+    <t>ZXGD3002E6TA</t>
   </si>
   <si>
     <t>Manufacturer</t>
   </si>
   <si>
+    <t>KNSCHA</t>
+  </si>
+  <si>
+    <t>CCTC</t>
+  </si>
+  <si>
     <t>Yageo</t>
   </si>
   <si>
+    <t>Dersonic</t>
+  </si>
+  <si>
+    <t>Taiyo Yuden</t>
+  </si>
+  <si>
+    <t>MDD</t>
+  </si>
+  <si>
+    <t>BHFUSE</t>
+  </si>
+  <si>
+    <t>Phoenix Contact</t>
+  </si>
+  <si>
+    <t>HCTL</t>
+  </si>
+  <si>
+    <t>XKB Connectivity</t>
+  </si>
+  <si>
+    <t>XUNPU</t>
+  </si>
+  <si>
+    <t>PROD Tech</t>
+  </si>
+  <si>
+    <t>SXN</t>
+  </si>
+  <si>
+    <t>Foshan NationStar Optoelectronics</t>
+  </si>
+  <si>
+    <t>BORN</t>
+  </si>
+  <si>
+    <t>Diodes Zetex</t>
+  </si>
+  <si>
+    <t>VBsemi</t>
+  </si>
+  <si>
+    <t>GoFord</t>
+  </si>
+  <si>
+    <t>Vishay</t>
+  </si>
+  <si>
+    <t>Huaxing Mechanical-Elec</t>
+  </si>
+  <si>
+    <t>BOCHEN</t>
+  </si>
+  <si>
+    <t>CCO</t>
+  </si>
+  <si>
+    <t>UMW</t>
+  </si>
+  <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
+    <t>STMicroelectronics</t>
+  </si>
+  <si>
+    <t>LCSC Part Number</t>
+  </si>
+  <si>
+    <t>C7471889</t>
+  </si>
+  <si>
+    <t>C6266891</t>
+  </si>
+  <si>
+    <t>C7471881</t>
+  </si>
+  <si>
+    <t>C309478</t>
+  </si>
+  <si>
+    <t>C20754717</t>
+  </si>
+  <si>
+    <t>C90143</t>
+  </si>
+  <si>
+    <t>C710687</t>
+  </si>
+  <si>
+    <t>C2761745</t>
+  </si>
+  <si>
+    <t>C3011128</t>
+  </si>
+  <si>
+    <t>C883154</t>
+  </si>
+  <si>
+    <t>C480516</t>
+  </si>
+  <si>
+    <t>C2908597</t>
+  </si>
+  <si>
+    <t>C319122</t>
+  </si>
+  <si>
+    <t>C3029440</t>
+  </si>
+  <si>
+    <t>C2983094</t>
+  </si>
+  <si>
+    <t>C400317</t>
+  </si>
+  <si>
+    <t>C158100</t>
+  </si>
+  <si>
+    <t>C344010</t>
+  </si>
+  <si>
+    <t>C460141</t>
+  </si>
+  <si>
+    <t>C5179533</t>
+  </si>
+  <si>
+    <t>C840062</t>
+  </si>
+  <si>
+    <t>C95781</t>
+  </si>
+  <si>
+    <t>C844922</t>
+  </si>
+  <si>
+    <t>C713997</t>
+  </si>
+  <si>
+    <t>C118907</t>
+  </si>
+  <si>
+    <t>C96346</t>
+  </si>
+  <si>
+    <t>C137067</t>
+  </si>
+  <si>
+    <t>C859155</t>
+  </si>
+  <si>
+    <t>C119328</t>
+  </si>
+  <si>
+    <t>C95204</t>
+  </si>
+  <si>
+    <t>C114623</t>
+  </si>
+  <si>
+    <t>C114668</t>
+  </si>
+  <si>
+    <t>C705836</t>
+  </si>
+  <si>
+    <t>C5185875</t>
+  </si>
+  <si>
+    <t>C32699</t>
+  </si>
+  <si>
+    <t>C880084</t>
+  </si>
+  <si>
+    <t>C156276</t>
+  </si>
+  <si>
+    <t>470uF</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>220uF</t>
+  </si>
+  <si>
+    <t>2.2uF</t>
+  </si>
+  <si>
+    <t>47nF</t>
+  </si>
+  <si>
+    <t>100uF</t>
+  </si>
+  <si>
+    <t>10nF</t>
+  </si>
+  <si>
+    <t>220pF</t>
+  </si>
+  <si>
+    <t>68uH</t>
+  </si>
+  <si>
+    <t>220uH</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>1M</t>
+  </si>
+  <si>
+    <t>DNP</t>
+  </si>
+  <si>
+    <t>100K</t>
+  </si>
+  <si>
+    <t>10R</t>
+  </si>
+  <si>
+    <t>1.5K</t>
+  </si>
+  <si>
+    <t>10K</t>
+  </si>
+  <si>
+    <t>47R</t>
+  </si>
+  <si>
+    <t>270R</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Bill of Materials for Project [Oil-Diffuser-A-v1.0.0.]</t>
+  </si>
+  <si>
+    <t>Oil-Diffuser-A-v1.0.0.</t>
+  </si>
+  <si>
+    <t>Alternate Part Number</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>MOQ (1 Boards)</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Unit Cost (1 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (1 Boards)</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>DO NOT PLACE</t>
+  </si>
+  <si>
+    <t>GCM188R91H103KA37D</t>
+  </si>
+  <si>
     <t>Murata</t>
   </si>
   <si>
-    <t>Ymin</t>
-  </si>
-  <si>
-    <t>Hongzhi Elec</t>
-  </si>
-  <si>
-    <t>Taiyo Yuden</t>
-  </si>
-  <si>
-    <t>MDD</t>
-  </si>
-  <si>
-    <t>Shenzhen JDT Fuse</t>
-  </si>
-  <si>
-    <t>Phoenix Contact</t>
-  </si>
-  <si>
-    <t>XKB Connectivity</t>
-  </si>
-  <si>
-    <t>XUNPU</t>
-  </si>
-  <si>
-    <t>HCTL</t>
-  </si>
-  <si>
-    <t>TDK</t>
-  </si>
-  <si>
-    <t>Foshan NationStar Optoelectronics</t>
-  </si>
-  <si>
-    <t>Infineon</t>
-  </si>
-  <si>
-    <t>Vishay Dale</t>
-  </si>
-  <si>
-    <t>BOURNS</t>
-  </si>
-  <si>
-    <t>STMicroelectronics</t>
-  </si>
-  <si>
-    <t>XBLW</t>
-  </si>
-  <si>
-    <t>LCSC Part Number</t>
-  </si>
-  <si>
-    <t>C113803</t>
-  </si>
-  <si>
-    <t>C162686</t>
-  </si>
-  <si>
-    <t>C487409</t>
-  </si>
-  <si>
-    <t>C333838</t>
-  </si>
-  <si>
-    <t>C90143</t>
-  </si>
-  <si>
-    <t>C710687</t>
-  </si>
-  <si>
-    <t>C3011128</t>
-  </si>
-  <si>
-    <t>C136343</t>
-  </si>
-  <si>
-    <t>C480516</t>
-  </si>
-  <si>
-    <t>C319122</t>
-  </si>
-  <si>
-    <t>C3029440</t>
-  </si>
-  <si>
-    <t>C2908597</t>
-  </si>
-  <si>
-    <t>C404509</t>
-  </si>
-  <si>
-    <t>C158100</t>
-  </si>
-  <si>
-    <t>C95781</t>
-  </si>
-  <si>
-    <t>C108080</t>
-  </si>
-  <si>
-    <t>C844917</t>
-  </si>
-  <si>
-    <t>C116296</t>
-  </si>
-  <si>
-    <t>C114669</t>
-  </si>
-  <si>
-    <t>C915681</t>
-  </si>
-  <si>
-    <t>C18723595</t>
-  </si>
-  <si>
-    <t>0.1uF</t>
-  </si>
-  <si>
-    <t>100uF</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>10nF</t>
-  </si>
-  <si>
-    <t>220uH</t>
-  </si>
-  <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>10R</t>
-  </si>
-  <si>
-    <t>100R</t>
-  </si>
-  <si>
-    <t>DNP</t>
-  </si>
-  <si>
-    <t>470R</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Bill of Materials for Project [Oil-Diffuser-A-v1.0.0}</t>
-  </si>
-  <si>
-    <t>Oil-Diffuser-A-v1.0.0</t>
-  </si>
-  <si>
-    <t>Alternate Part Number</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Links</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>Quantity (3 Boards)</t>
+    <t>Quantity (3 Boads)</t>
   </si>
   <si>
     <t>MOQ (3 Boards)</t>
@@ -521,103 +793,127 @@
     <t>Total Cost (3 Boards)</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>DO NOT PLACE</t>
-  </si>
-  <si>
-    <t>C2583</t>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>100</t>
   </si>
   <si>
-    <t>5</t>
+    <t>50</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>LCSC</t>
-  </si>
-  <si>
-    <t>0.0043</t>
-  </si>
-  <si>
-    <t>0.6424</t>
-  </si>
-  <si>
-    <t>0.1625</t>
-  </si>
-  <si>
-    <t>0.0341</t>
-  </si>
-  <si>
-    <t>0.4566</t>
+    <t>0.1516</t>
+  </si>
+  <si>
+    <t>0.0039</t>
+  </si>
+  <si>
+    <t>0.0880</t>
+  </si>
+  <si>
+    <t>0.0171</t>
+  </si>
+  <si>
+    <t>0.0263</t>
+  </si>
+  <si>
+    <t>0.4461</t>
   </si>
   <si>
     <t>0.0313</t>
   </si>
   <si>
+    <t>0.0326</t>
+  </si>
+  <si>
     <t>0.0594</t>
   </si>
   <si>
-    <t>0.0279</t>
+    <t>0.0687</t>
   </si>
   <si>
     <t>0.3559</t>
   </si>
   <si>
+    <t>0.0143</t>
+  </si>
+  <si>
     <t>0.1350</t>
   </si>
   <si>
-    <t>0.0480</t>
-  </si>
-  <si>
-    <t>0.0143</t>
-  </si>
-  <si>
-    <t>0.1082</t>
-  </si>
-  <si>
-    <t>0.0253</t>
-  </si>
-  <si>
-    <t>0.2374</t>
+    <t>0.1463</t>
+  </si>
+  <si>
+    <t>0.0850</t>
+  </si>
+  <si>
+    <t>0.0249</t>
+  </si>
+  <si>
+    <t>0.0453</t>
+  </si>
+  <si>
+    <t>0.0496</t>
+  </si>
+  <si>
+    <t>0.2876</t>
+  </si>
+  <si>
+    <t>0.0897</t>
   </si>
   <si>
     <t>0.0018</t>
   </si>
   <si>
-    <t>0.0088</t>
-  </si>
-  <si>
-    <t>0.0031</t>
-  </si>
-  <si>
-    <t>0.0012</t>
-  </si>
-  <si>
-    <t>0.1153</t>
-  </si>
-  <si>
-    <t>0.0303</t>
-  </si>
-  <si>
-    <t>GCM188R91H103KA37D</t>
-  </si>
-  <si>
-    <t>Murata Electronics</t>
-  </si>
-  <si>
-    <t>Custom</t>
+    <t>0.0034</t>
+  </si>
+  <si>
+    <t>0.0062</t>
+  </si>
+  <si>
+    <t>0.0021</t>
+  </si>
+  <si>
+    <t>0.0430</t>
+  </si>
+  <si>
+    <t>0.0112</t>
+  </si>
+  <si>
+    <t>0.0095</t>
+  </si>
+  <si>
+    <t>0.0207</t>
+  </si>
+  <si>
+    <t>0.0011</t>
+  </si>
+  <si>
+    <t>0.0252</t>
+  </si>
+  <si>
+    <t>0.1487</t>
+  </si>
+  <si>
+    <t>0.2551</t>
+  </si>
+  <si>
+    <t>0.4769</t>
+  </si>
+  <si>
+    <t>0.4771</t>
+  </si>
+  <si>
+    <t>-----</t>
   </si>
   <si>
     <t>------</t>
@@ -626,37 +922,31 @@
     <t>Peripheral</t>
   </si>
   <si>
+    <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>AC 110v 240V DC 24V 2A Power Supply wall charger Adapter US Charger</t>
+  </si>
+  <si>
+    <t>24v 2 Amp US plug</t>
+  </si>
+  <si>
+    <t>AC 250V 6A On/Off Prewired Standard Toggle Switch With Wire Cable KNS-1 SPST Contacts Switch Electrical Equipment</t>
+  </si>
+  <si>
     <t>Toggle Switch</t>
   </si>
   <si>
-    <t>AC 250V 6A On/Off Prewired Standard Toggle Switch With Wire Cable KNS-1 SPST Contacts Switch Electrical Equipment</t>
-  </si>
-  <si>
-    <t>Aliexpress</t>
-  </si>
-  <si>
-    <t>1Pcs Gdstime DC 5V 12V 24V 75mm x 30mm Centrifugal Blower Fan 7530 7.5cm Dual Ball Turbo Radiator Fan 75mm Purifier Heatsink Fan</t>
-  </si>
-  <si>
-    <t>Blower Fan</t>
-  </si>
-  <si>
-    <t>Charger</t>
-  </si>
-  <si>
-    <t>24V0.5A New AC 100V-240V Converter Switching Power Adapter DC 24V 0.5A 500mA Universla Power Supply EU Plug Tablet Charger</t>
-  </si>
-  <si>
-    <t>±10% 50V 100nF X7R Plugin,P=2.54mm Multilayer Ceramic Capacitors MLCC - Leaded ROHS</t>
-  </si>
-  <si>
-    <t>178MU0006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KNSCHA </t>
-  </si>
-  <si>
-    <t>C5632430</t>
+    <t>24V Sleeve XH2.54</t>
+  </si>
+  <si>
+    <t>1Pcs Gdstime DC 24V 75mm x 30mm Centrifugal Blower Fan 7530 7.5cm Dual Ball Turbo Radiator Fan 75mm Purifier Heatsink Fan</t>
+  </si>
+  <si>
+    <t>16mm 1.7MHz</t>
+  </si>
+  <si>
+    <t>D16mm 1.7MHz Ultrasonic Mist Maker Atomizing Transducer Ceramic Humidifier</t>
   </si>
 </sst>
 </file>
@@ -668,7 +958,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -819,11 +1109,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color indexed="12"/>
@@ -839,7 +1124,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <strike/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1019,14 +1305,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1131,36 +1416,44 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1172,227 +1465,37 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </horizontal>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
-    </tableStyle>
-  </tableStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
       <color rgb="FF03A4CB"/>
@@ -1673,25 +1776,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q34"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:Q62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" customWidth="1"/>
-    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" customWidth="1"/>
     <col min="15" max="15" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" thickBot="1">
@@ -1705,13 +1809,13 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
     </row>
     <row r="2" spans="1:17" ht="32.25" thickBot="1">
       <c r="A2" s="1"/>
@@ -1722,7 +1826,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="40" t="s">
-        <v>156</v>
+        <v>239</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="3"/>
@@ -1745,7 +1849,7 @@
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="41" t="s">
-        <v>157</v>
+        <v>240</v>
       </c>
       <c r="G3" s="29"/>
       <c r="H3" s="30"/>
@@ -1759,7 +1863,7 @@
       <c r="P3" s="24"/>
       <c r="Q3" s="24"/>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" ht="15" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="8"/>
       <c r="C4" s="26"/>
@@ -1778,7 +1882,7 @@
       <c r="P4" s="24"/>
       <c r="Q4" s="24"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" ht="15" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="9"/>
       <c r="C5" s="33"/>
@@ -1797,7 +1901,7 @@
       <c r="P5" s="35"/>
       <c r="Q5" s="35"/>
     </row>
-    <row r="6" spans="1:17" ht="15.75" thickBot="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" thickBot="1">
       <c r="A6" s="1"/>
       <c r="B6" s="11"/>
       <c r="C6" s="36"/>
@@ -1825,49 +1929,49 @@
         <v>5</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>158</v>
+        <v>241</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>159</v>
+        <v>242</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>163</v>
+        <v>243</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>160</v>
+        <v>244</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>164</v>
+        <v>245</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>165</v>
+        <v>246</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="48">
       <c r="A8" s="1"/>
       <c r="B8" s="16">
         <f>ROW(B8) - ROW($B$7)</f>
@@ -1877,95 +1981,95 @@
         <v>6</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>71</v>
+        <v>248</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I8" s="50" t="s">
-        <v>199</v>
+        <v>156</v>
+      </c>
+      <c r="I8" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>145</v>
+        <v>219</v>
       </c>
       <c r="L8" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="N8" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="O8" s="21" t="s">
-        <v>175</v>
+        <v>258</v>
+      </c>
+      <c r="N8" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>263</v>
       </c>
       <c r="P8" s="15">
         <f>O8*M8</f>
-        <v>0.43</v>
+        <v>0.75800000000000001</v>
       </c>
       <c r="Q8" s="14"/>
     </row>
-    <row r="9" spans="1:17" ht="48">
+    <row r="9" spans="1:17" ht="36">
       <c r="A9" s="1"/>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B29" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B48" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>198</v>
+        <v>63</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>101</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>209</v>
+        <v>130</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="I9" s="50" t="s">
-        <v>199</v>
+        <v>157</v>
+      </c>
+      <c r="I9" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="K9" s="20" t="s">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="L9" s="20">
-        <v>1</v>
-      </c>
-      <c r="M9" s="14">
-        <v>50</v>
-      </c>
-      <c r="N9" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="O9" s="21">
-        <v>1.1900000000000001E-2</v>
-      </c>
-      <c r="P9" s="21">
-        <f t="shared" ref="P9" si="1">O9*M9</f>
-        <v>0.59500000000000008</v>
+        <v>2</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="N9" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O9" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="P9" s="15">
+        <f t="shared" ref="P9:P43" si="1">O9*M9</f>
+        <v>0.38999999999999996</v>
       </c>
       <c r="Q9" s="20"/>
     </row>
@@ -1979,197 +2083,197 @@
         <v>6</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="I10" s="50" t="s">
-        <v>199</v>
+        <v>156</v>
+      </c>
+      <c r="I10" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>126</v>
+        <v>184</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>146</v>
+        <v>221</v>
       </c>
       <c r="L10" s="14">
         <v>1</v>
       </c>
-      <c r="M10" s="14">
-        <v>2</v>
-      </c>
-      <c r="N10" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="O10" s="21" t="s">
-        <v>177</v>
+      <c r="M10" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="N10" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>265</v>
       </c>
       <c r="P10" s="15">
-        <f>O10*M10</f>
-        <v>0.32500000000000001</v>
+        <f t="shared" si="1"/>
+        <v>0.43999999999999995</v>
       </c>
       <c r="Q10" s="14"/>
     </row>
-    <row r="11" spans="1:17" ht="36">
+    <row r="11" spans="1:17">
       <c r="A11" s="1"/>
       <c r="B11" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>198</v>
+        <v>65</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>103</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="I11" s="50" t="s">
-        <v>199</v>
+        <v>158</v>
+      </c>
+      <c r="I11" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>127</v>
+        <v>185</v>
       </c>
       <c r="K11" s="20" t="s">
-        <v>147</v>
+        <v>222</v>
       </c>
       <c r="L11" s="20">
         <v>1</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="N11" s="48" t="s">
-        <v>174</v>
+        <v>260</v>
+      </c>
+      <c r="N11" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="O11" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="P11" s="21">
-        <f t="shared" ref="P11" si="2">O11*M11</f>
-        <v>0.34099999999999997</v>
+        <v>266</v>
+      </c>
+      <c r="P11" s="15">
+        <f t="shared" si="1"/>
+        <v>0.85499999999999998</v>
       </c>
       <c r="Q11" s="20"/>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" ht="24">
       <c r="A12" s="1"/>
       <c r="B12" s="16">
         <f>ROW(B12) - ROW($B$7)</f>
         <v>5</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>75</v>
+        <v>248</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="I12" s="50" t="s">
-        <v>199</v>
+        <v>159</v>
+      </c>
+      <c r="I12" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>128</v>
+        <v>186</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>146</v>
+        <v>223</v>
       </c>
       <c r="L12" s="14">
         <v>1</v>
       </c>
-      <c r="M12" s="14">
-        <v>2</v>
-      </c>
-      <c r="N12" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="O12" s="21" t="s">
-        <v>179</v>
+      <c r="M12" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="N12" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O12" s="15" t="s">
+        <v>267</v>
       </c>
       <c r="P12" s="15">
-        <f>O12*M12</f>
-        <v>0.91320000000000001</v>
+        <f t="shared" si="1"/>
+        <v>0.52600000000000002</v>
       </c>
       <c r="Q12" s="14"/>
     </row>
-    <row r="13" spans="1:17" ht="24">
+    <row r="13" spans="1:17">
       <c r="A13" s="1"/>
       <c r="B13" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>196</v>
+        <v>132</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="I13" s="50" t="s">
-        <v>199</v>
+        <v>160</v>
+      </c>
+      <c r="I13" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>129</v>
+        <v>187</v>
       </c>
       <c r="K13" s="20" t="s">
-        <v>148</v>
+        <v>224</v>
       </c>
       <c r="L13" s="20">
         <v>1</v>
       </c>
-      <c r="M13" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="N13" s="46" t="s">
-        <v>174</v>
+      <c r="M13" s="14">
+        <v>2</v>
+      </c>
+      <c r="N13" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="O13" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="P13" s="21">
-        <f t="shared" ref="P13" si="3">O13*M13</f>
-        <v>0.626</v>
+        <v>268</v>
+      </c>
+      <c r="P13" s="15">
+        <f t="shared" si="1"/>
+        <v>0.89219999999999999</v>
       </c>
       <c r="Q13" s="20"/>
     </row>
@@ -2180,47 +2284,47 @@
         <v>7</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="I14" s="50" t="s">
-        <v>199</v>
+        <v>101</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="I14" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>166</v>
+        <v>225</v>
       </c>
       <c r="L14" s="14">
         <v>1</v>
       </c>
       <c r="M14" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="N14" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="O14" s="21" t="s">
-        <v>181</v>
+        <v>261</v>
+      </c>
+      <c r="N14" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O14" s="15" t="s">
+        <v>269</v>
       </c>
       <c r="P14" s="15">
-        <f>O14*M14</f>
-        <v>0.59399999999999997</v>
+        <f t="shared" si="1"/>
+        <v>0.626</v>
       </c>
       <c r="Q14" s="14"/>
     </row>
@@ -2231,609 +2335,609 @@
         <v>8</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>77</v>
+        <v>69</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>248</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="I15" s="50" t="s">
-        <v>199</v>
+        <v>159</v>
+      </c>
+      <c r="I15" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="K15" s="14" t="s">
-        <v>166</v>
+        <v>189</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>226</v>
       </c>
       <c r="L15" s="20">
         <v>1</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="N15" s="48" t="s">
-        <v>174</v>
+        <v>261</v>
+      </c>
+      <c r="N15" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="O15" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="P15" s="21">
-        <f t="shared" ref="P15" si="4">O15*M15</f>
-        <v>0.55800000000000005</v>
+        <v>270</v>
+      </c>
+      <c r="P15" s="15">
+        <f t="shared" si="1"/>
+        <v>0.65199999999999991</v>
       </c>
       <c r="Q15" s="20"/>
     </row>
-    <row r="16" spans="1:17" ht="24">
+    <row r="16" spans="1:17">
       <c r="A16" s="1"/>
       <c r="B16" s="16">
         <f>ROW(B16) - ROW($B$7)</f>
         <v>9</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="G16" s="14">
-        <v>1715721</v>
+        <v>107</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>133</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="I16" s="50" t="s">
-        <v>199</v>
+        <v>161</v>
+      </c>
+      <c r="I16" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="L16" s="14">
-        <v>1</v>
-      </c>
-      <c r="M16" s="14">
         <v>2</v>
       </c>
-      <c r="N16" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="O16" s="21" t="s">
-        <v>183</v>
+      <c r="M16" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="N16" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O16" s="15" t="s">
+        <v>271</v>
       </c>
       <c r="P16" s="15">
-        <f>O16*M16</f>
-        <v>0.71179999999999999</v>
+        <f t="shared" si="1"/>
+        <v>0.59399999999999997</v>
       </c>
       <c r="Q16" s="14"/>
     </row>
-    <row r="17" spans="1:17" ht="48">
+    <row r="17" spans="1:17" ht="24">
       <c r="A17" s="1"/>
       <c r="B17" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>198</v>
+        <v>71</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>108</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="I17" s="50" t="s">
-        <v>199</v>
+        <v>162</v>
+      </c>
+      <c r="I17" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="L17" s="20">
         <v>1</v>
       </c>
       <c r="M17" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="N17" s="48" t="s">
-        <v>174</v>
+        <v>258</v>
+      </c>
+      <c r="N17" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="O17" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="P17" s="21">
-        <f t="shared" ref="P17" si="5">O17*M17</f>
-        <v>0.67500000000000004</v>
+        <v>272</v>
+      </c>
+      <c r="P17" s="15">
+        <f t="shared" si="1"/>
+        <v>0.34349999999999997</v>
       </c>
       <c r="Q17" s="20"/>
     </row>
-    <row r="18" spans="1:17" ht="48">
+    <row r="18" spans="1:17">
       <c r="A18" s="1"/>
       <c r="B18" s="16">
         <f>ROW(B18) - ROW($B$7)</f>
         <v>11</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>79</v>
+        <v>248</v>
+      </c>
+      <c r="G18" s="14">
+        <v>1715721</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="I18" s="50" t="s">
-        <v>199</v>
+        <v>163</v>
+      </c>
+      <c r="I18" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="L18" s="14">
         <v>1</v>
       </c>
-      <c r="M18" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="N18" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="O18" s="21" t="s">
-        <v>185</v>
+      <c r="M18" s="14">
+        <v>2</v>
+      </c>
+      <c r="N18" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O18" s="15" t="s">
+        <v>273</v>
       </c>
       <c r="P18" s="15">
-        <f>O18*M18</f>
-        <v>0.48</v>
+        <f t="shared" si="1"/>
+        <v>0.71179999999999999</v>
       </c>
       <c r="Q18" s="14"/>
     </row>
-    <row r="19" spans="1:17" ht="48">
+    <row r="19" spans="1:17" ht="36">
       <c r="A19" s="1"/>
       <c r="B19" s="17">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="I19" s="50" t="s">
-        <v>199</v>
+        <v>164</v>
+      </c>
+      <c r="I19" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="L19" s="20">
         <v>1</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="N19" s="48" t="s">
-        <v>174</v>
+        <v>260</v>
+      </c>
+      <c r="N19" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="O19" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="P19" s="21">
-        <f t="shared" ref="P19" si="6">O19*M19</f>
+        <v>274</v>
+      </c>
+      <c r="P19" s="15">
+        <f t="shared" si="1"/>
         <v>0.71499999999999997</v>
       </c>
       <c r="Q19" s="20"/>
     </row>
-    <row r="20" spans="1:17" ht="24">
+    <row r="20" spans="1:17" ht="36">
       <c r="A20" s="1"/>
       <c r="B20" s="16">
         <f>ROW(B20) - ROW($B$7)</f>
         <v>13</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="I20" s="50" t="s">
-        <v>199</v>
+        <v>165</v>
+      </c>
+      <c r="I20" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>149</v>
+        <v>249</v>
       </c>
       <c r="L20" s="14">
         <v>1</v>
       </c>
       <c r="M20" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="N20" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="O20" s="21" t="s">
-        <v>187</v>
+        <v>258</v>
+      </c>
+      <c r="N20" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O20" s="15" t="s">
+        <v>275</v>
       </c>
       <c r="P20" s="15">
-        <f>O20*M20</f>
-        <v>0.54100000000000004</v>
+        <f t="shared" si="1"/>
+        <v>0.67500000000000004</v>
       </c>
       <c r="Q20" s="14"/>
     </row>
-    <row r="21" spans="1:17" ht="48">
+    <row r="21" spans="1:17" ht="36">
       <c r="A21" s="1"/>
       <c r="B21" s="17">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="H21" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="I21" s="50" t="s">
-        <v>199</v>
-      </c>
-      <c r="J21" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="K21" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="59" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="59" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="G21" s="59" t="s">
+        <v>111</v>
+      </c>
+      <c r="H21" s="59" t="s">
         <v>166</v>
       </c>
-      <c r="L21" s="20">
-        <v>1</v>
-      </c>
-      <c r="M21" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="N21" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="O21" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="P21" s="21">
-        <f t="shared" ref="P21" si="7">O21*M21</f>
-        <v>0.50600000000000001</v>
-      </c>
-      <c r="Q21" s="20"/>
-    </row>
-    <row r="22" spans="1:17" ht="25.5">
+      <c r="I21" s="62" t="s">
+        <v>297</v>
+      </c>
+      <c r="J21" s="59" t="s">
+        <v>195</v>
+      </c>
+      <c r="K21" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="L21" s="59">
+        <v>1</v>
+      </c>
+      <c r="M21" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="N21" s="60" t="s">
+        <v>257</v>
+      </c>
+      <c r="O21" s="61" t="s">
+        <v>249</v>
+      </c>
+      <c r="P21" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q21" s="63" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="24">
       <c r="A22" s="1"/>
       <c r="B22" s="16">
         <f>ROW(B22) - ROW($B$7)</f>
         <v>15</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="F22" s="47" t="s">
-        <v>198</v>
-      </c>
-      <c r="G22" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="H22" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="I22" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="J22" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="K22" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="L22" s="47">
-        <v>2</v>
-      </c>
-      <c r="M22" s="47">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="I22" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="L22" s="14">
+        <v>1</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>258</v>
       </c>
       <c r="N22" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="O22" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="P22" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q22" s="45" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17">
+        <v>257</v>
+      </c>
+      <c r="O22" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="P22" s="15">
+        <f t="shared" si="1"/>
+        <v>0.73150000000000004</v>
+      </c>
+      <c r="Q22" s="14"/>
+    </row>
+    <row r="23" spans="1:17" ht="24">
       <c r="A23" s="1"/>
       <c r="B23" s="17">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>83</v>
+        <v>77</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>248</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="I23" s="50" t="s">
-        <v>199</v>
+        <v>168</v>
+      </c>
+      <c r="I23" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="K23" s="20" t="s">
-        <v>166</v>
+        <v>228</v>
       </c>
       <c r="L23" s="20">
         <v>1</v>
       </c>
       <c r="M23" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="N23" s="48" t="s">
-        <v>174</v>
+        <v>258</v>
+      </c>
+      <c r="N23" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="O23" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="P23" s="21">
-        <f t="shared" ref="P23" si="8">O23*M23</f>
-        <v>1.1870000000000001</v>
+        <v>277</v>
+      </c>
+      <c r="P23" s="15">
+        <f t="shared" si="1"/>
+        <v>0.42500000000000004</v>
       </c>
       <c r="Q23" s="20"/>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" ht="24">
       <c r="A24" s="1"/>
       <c r="B24" s="16">
         <f>ROW(B24) - ROW($B$7)</f>
         <v>17</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="50" t="s">
-        <v>199</v>
+        <v>169</v>
+      </c>
+      <c r="I24" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>138</v>
+        <v>198</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>150</v>
+        <v>249</v>
       </c>
       <c r="L24" s="14">
         <v>1</v>
       </c>
       <c r="M24" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="N24" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="O24" s="21" t="s">
-        <v>190</v>
+        <v>261</v>
+      </c>
+      <c r="N24" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O24" s="15" t="s">
+        <v>278</v>
       </c>
       <c r="P24" s="15">
-        <f>O24*M24</f>
-        <v>0.18</v>
+        <f t="shared" si="1"/>
+        <v>0.498</v>
       </c>
       <c r="Q24" s="14"/>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:17" ht="36">
       <c r="A25" s="1"/>
       <c r="B25" s="17">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="I25" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="I25" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J25" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="J25" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="K25" s="20" t="s">
-        <v>151</v>
+      <c r="K25" s="14" t="s">
+        <v>249</v>
       </c>
       <c r="L25" s="20">
         <v>1</v>
       </c>
       <c r="M25" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="N25" s="48" t="s">
-        <v>174</v>
+        <v>262</v>
+      </c>
+      <c r="N25" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="O25" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="P25" s="21">
-        <f t="shared" ref="P25" si="9">O25*M25</f>
-        <v>0.44</v>
+        <v>279</v>
+      </c>
+      <c r="P25" s="15">
+        <f t="shared" si="1"/>
+        <v>0.45300000000000001</v>
       </c>
       <c r="Q25" s="20"/>
     </row>
-    <row r="26" spans="1:17" ht="24">
+    <row r="26" spans="1:17">
       <c r="A26" s="1"/>
       <c r="B26" s="16">
         <f>ROW(B26) - ROW($B$7)</f>
         <v>19</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="I26" s="50" t="s">
-        <v>199</v>
+        <v>171</v>
+      </c>
+      <c r="I26" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>152</v>
+        <v>249</v>
       </c>
       <c r="L26" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="N26" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="O26" s="21" t="s">
-        <v>192</v>
+        <v>262</v>
+      </c>
+      <c r="N26" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O26" s="15" t="s">
+        <v>280</v>
       </c>
       <c r="P26" s="15">
-        <f>O26*M26</f>
-        <v>0.31</v>
+        <f t="shared" si="1"/>
+        <v>0.496</v>
       </c>
       <c r="Q26" s="14"/>
     </row>
@@ -2844,150 +2948,149 @@
         <v>20</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" s="47" t="s">
-        <v>198</v>
-      </c>
-      <c r="G27" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="H27" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="I27" s="50" t="s">
-        <v>199</v>
-      </c>
-      <c r="J27" s="42" t="s">
-        <v>141</v>
-      </c>
-      <c r="K27" s="42" t="s">
-        <v>153</v>
-      </c>
-      <c r="L27" s="42">
-        <v>1</v>
-      </c>
-      <c r="M27" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="N27" s="49" t="s">
-        <v>166</v>
-      </c>
-      <c r="O27" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="P27" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q27" s="45" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17">
+        <v>18</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="I27" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="L27" s="20">
+        <v>1</v>
+      </c>
+      <c r="M27" s="14">
+        <v>2</v>
+      </c>
+      <c r="N27" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O27" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="P27" s="15">
+        <f t="shared" si="1"/>
+        <v>0.57520000000000004</v>
+      </c>
+      <c r="Q27" s="20"/>
+    </row>
+    <row r="28" spans="1:17" ht="24">
       <c r="A28" s="1"/>
       <c r="B28" s="16">
         <f>ROW(B28) - ROW($B$7)</f>
         <v>21</v>
       </c>
-      <c r="C28" s="23" t="s">
-        <v>18</v>
+      <c r="C28" s="22" t="s">
+        <v>16</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I28" s="50" t="s">
-        <v>199</v>
+        <v>173</v>
+      </c>
+      <c r="I28" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>154</v>
+        <v>249</v>
       </c>
       <c r="L28" s="14">
         <v>1</v>
       </c>
       <c r="M28" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="N28" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="O28" s="21" t="s">
-        <v>193</v>
+        <v>258</v>
+      </c>
+      <c r="N28" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O28" s="15" t="s">
+        <v>282</v>
       </c>
       <c r="P28" s="15">
-        <f>O28*M28</f>
-        <v>0.12</v>
+        <f t="shared" si="1"/>
+        <v>0.44850000000000001</v>
       </c>
       <c r="Q28" s="14"/>
     </row>
-    <row r="29" spans="1:17" ht="24">
+    <row r="29" spans="1:17">
       <c r="A29" s="1"/>
       <c r="B29" s="17">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="I29" s="50" t="s">
-        <v>199</v>
+        <v>158</v>
+      </c>
+      <c r="I29" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="K29" s="20" t="s">
-        <v>166</v>
+        <v>229</v>
       </c>
       <c r="L29" s="20">
         <v>1</v>
       </c>
       <c r="M29" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="N29" s="48" t="s">
-        <v>174</v>
+        <v>259</v>
+      </c>
+      <c r="N29" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="O29" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="P29" s="21">
-        <f t="shared" ref="P29" si="10">O29*M29</f>
-        <v>0.57650000000000001</v>
+        <v>283</v>
+      </c>
+      <c r="P29" s="15">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
       </c>
       <c r="Q29" s="20"/>
     </row>
@@ -2998,287 +3101,1090 @@
         <v>23</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="I30" s="50" t="s">
-        <v>199</v>
+        <v>174</v>
+      </c>
+      <c r="I30" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="K30" s="20" t="s">
-        <v>166</v>
+        <v>204</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>230</v>
       </c>
       <c r="L30" s="14">
         <v>1</v>
       </c>
       <c r="M30" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="N30" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="O30" s="21" t="s">
-        <v>195</v>
+        <v>259</v>
+      </c>
+      <c r="N30" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O30" s="15" t="s">
+        <v>284</v>
       </c>
       <c r="P30" s="15">
-        <f>O30*M30</f>
-        <v>0.30299999999999999</v>
+        <f t="shared" si="1"/>
+        <v>0.33999999999999997</v>
       </c>
       <c r="Q30" s="14"/>
     </row>
-    <row r="31" spans="1:17" ht="48">
+    <row r="31" spans="1:17" ht="36">
       <c r="A31" s="1"/>
-      <c r="B31" s="16">
-        <f>ROW(B31) - ROW($B$7)</f>
+      <c r="B31" s="17">
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C31" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="I31" s="50" t="s">
-        <v>166</v>
-      </c>
-      <c r="J31" s="14" t="s">
-        <v>166</v>
+      <c r="C31" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="I31" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>205</v>
       </c>
       <c r="K31" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="L31" s="14">
-        <v>1</v>
-      </c>
-      <c r="M31" s="14">
-        <v>1</v>
-      </c>
-      <c r="N31" s="48" t="s">
-        <v>203</v>
-      </c>
-      <c r="O31" s="21">
-        <v>1.1499999999999999</v>
+        <v>229</v>
+      </c>
+      <c r="L31" s="20">
+        <v>1</v>
+      </c>
+      <c r="M31" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="N31" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O31" s="21" t="s">
+        <v>285</v>
       </c>
       <c r="P31" s="15">
-        <f>O31*M31</f>
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="Q31" s="14"/>
-    </row>
-    <row r="32" spans="1:17" ht="60">
+        <f t="shared" si="1"/>
+        <v>0.62</v>
+      </c>
+      <c r="Q31" s="20"/>
+    </row>
+    <row r="32" spans="1:17" ht="24">
       <c r="A32" s="1"/>
       <c r="B32" s="16">
-        <f t="shared" ref="B32:B33" si="11">ROW(B32) - ROW($B$7)</f>
+        <f>ROW(B32) - ROW($B$7)</f>
         <v>25</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="H32" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="I32" s="50" t="s">
-        <v>166</v>
-      </c>
-      <c r="J32" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="K32" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="L32" s="14">
-        <v>1</v>
-      </c>
-      <c r="M32" s="14">
-        <v>1</v>
-      </c>
-      <c r="N32" s="48" t="s">
-        <v>203</v>
-      </c>
-      <c r="O32" s="21">
-        <v>13.58</v>
-      </c>
-      <c r="P32" s="15">
-        <f>O32*M32</f>
-        <v>13.58</v>
-      </c>
-      <c r="Q32" s="14"/>
-    </row>
-    <row r="33" spans="1:17" ht="60.75" thickBot="1">
+        <v>21</v>
+      </c>
+      <c r="D32" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="F32" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="G32" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="H32" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="I32" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="J32" s="42" t="s">
+        <v>206</v>
+      </c>
+      <c r="K32" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="L32" s="42">
+        <v>2</v>
+      </c>
+      <c r="M32" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="N32" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="O32" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="P32" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q32" s="44" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
       <c r="A33" s="1"/>
-      <c r="B33" s="16">
-        <f t="shared" si="11"/>
+      <c r="B33" s="17">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C33" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="E33" s="14" t="s">
+      <c r="C33" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="H33" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="I33" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J33" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="F33" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="G33" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="H33" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="I33" s="50" t="s">
-        <v>166</v>
-      </c>
-      <c r="J33" s="14" t="s">
-        <v>166</v>
-      </c>
       <c r="K33" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="L33" s="14">
-        <v>1</v>
-      </c>
-      <c r="M33" s="14">
-        <v>1</v>
-      </c>
-      <c r="N33" s="48" t="s">
-        <v>203</v>
-      </c>
-      <c r="O33" s="21">
+        <v>232</v>
+      </c>
+      <c r="L33" s="20">
+        <v>1</v>
+      </c>
+      <c r="M33" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="N33" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O33" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="P33" s="15">
+        <f t="shared" si="1"/>
+        <v>0.21</v>
+      </c>
+      <c r="Q33" s="20"/>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" s="1"/>
+      <c r="B34" s="16">
+        <f>ROW(B34) - ROW($B$7)</f>
+        <v>27</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I34" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="L34" s="14">
+        <v>1</v>
+      </c>
+      <c r="M34" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="N34" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O34" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="P34" s="15">
+        <f t="shared" si="1"/>
+        <v>0.42999999999999994</v>
+      </c>
+      <c r="Q34" s="14"/>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35" s="1"/>
+      <c r="B35" s="17">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G35" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="H35" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="I35" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J35" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="K35" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="L35" s="20">
+        <v>1</v>
+      </c>
+      <c r="M35" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="N35" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O35" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="P35" s="15">
+        <f t="shared" si="1"/>
+        <v>0.55999999999999994</v>
+      </c>
+      <c r="Q35" s="20"/>
+    </row>
+    <row r="36" spans="1:17" ht="36">
+      <c r="A36" s="1"/>
+      <c r="B36" s="16">
+        <f>ROW(B36) - ROW($B$7)</f>
+        <v>29</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="I36" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="L36" s="14">
+        <v>1</v>
+      </c>
+      <c r="M36" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="N36" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O36" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="P36" s="15">
+        <f t="shared" si="1"/>
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="Q36" s="14"/>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" s="1"/>
+      <c r="B37" s="17">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="I37" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="K37" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="L37" s="20">
+        <v>1</v>
+      </c>
+      <c r="M37" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="N37" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O37" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="P37" s="15">
+        <f t="shared" si="1"/>
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="Q37" s="20"/>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" s="1"/>
+      <c r="B38" s="16">
+        <f>ROW(B38) - ROW($B$7)</f>
+        <v>31</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I38" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="L38" s="14">
+        <v>1</v>
+      </c>
+      <c r="M38" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="N38" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O38" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="P38" s="15">
+        <f t="shared" si="1"/>
+        <v>0.11</v>
+      </c>
+      <c r="Q38" s="14"/>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="A39" s="1"/>
+      <c r="B39" s="17">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="I39" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="K39" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="L39" s="20">
+        <v>2</v>
+      </c>
+      <c r="M39" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="N39" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O39" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="P39" s="15">
+        <f t="shared" si="1"/>
+        <v>0.11</v>
+      </c>
+      <c r="Q39" s="20"/>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40" s="1"/>
+      <c r="B40" s="16">
+        <f>ROW(B40) - ROW($B$7)</f>
+        <v>33</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I40" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="L40" s="14">
+        <v>1</v>
+      </c>
+      <c r="M40" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="N40" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O40" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="P40" s="15">
+        <f t="shared" si="1"/>
+        <v>0.504</v>
+      </c>
+      <c r="Q40" s="14"/>
+    </row>
+    <row r="41" spans="1:17" ht="24">
+      <c r="A41" s="1"/>
+      <c r="B41" s="17">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="H41" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="I41" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="K41" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L41" s="20">
+        <v>1</v>
+      </c>
+      <c r="M41" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="N41" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O41" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="P41" s="15">
+        <f t="shared" si="1"/>
+        <v>0.74350000000000005</v>
+      </c>
+      <c r="Q41" s="20"/>
+    </row>
+    <row r="42" spans="1:17" s="55" customFormat="1">
+      <c r="A42" s="48"/>
+      <c r="B42" s="49">
+        <f>ROW(B42) - ROW($B$7)</f>
+        <v>35</v>
+      </c>
+      <c r="C42" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="F42" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="G42" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="H42" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="I42" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J42" s="51" t="s">
+        <v>216</v>
+      </c>
+      <c r="K42" s="52" t="s">
+        <v>249</v>
+      </c>
+      <c r="L42" s="51">
+        <v>1</v>
+      </c>
+      <c r="M42" s="51" t="s">
+        <v>258</v>
+      </c>
+      <c r="N42" s="53" t="s">
+        <v>257</v>
+      </c>
+      <c r="O42" s="54" t="s">
+        <v>294</v>
+      </c>
+      <c r="P42" s="54">
+        <f t="shared" si="1"/>
+        <v>1.2755000000000001</v>
+      </c>
+      <c r="Q42" s="51"/>
+    </row>
+    <row r="43" spans="1:17" s="46" customFormat="1">
+      <c r="A43" s="45"/>
+      <c r="B43" s="17">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="H43" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="I43" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J43" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="K43" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L43" s="20">
+        <v>1</v>
+      </c>
+      <c r="M43" s="14">
+        <v>2</v>
+      </c>
+      <c r="N43" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O43" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="P43" s="15">
+        <f t="shared" si="1"/>
+        <v>0.95379999999999998</v>
+      </c>
+      <c r="Q43" s="20"/>
+    </row>
+    <row r="44" spans="1:17" s="46" customFormat="1">
+      <c r="A44" s="45"/>
+      <c r="B44" s="17">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C44" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="I44" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J44" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="K44" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L44" s="14">
+        <v>1</v>
+      </c>
+      <c r="M44" s="14">
+        <v>2</v>
+      </c>
+      <c r="N44" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="O44" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="P44" s="15">
+        <f>O44*M44</f>
+        <v>0.95420000000000005</v>
+      </c>
+      <c r="Q44" s="14"/>
+    </row>
+    <row r="45" spans="1:17" s="46" customFormat="1" ht="24.75">
+      <c r="A45" s="45"/>
+      <c r="B45" s="17">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="E45" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="I45" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J45" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="K45" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L45" s="14">
+        <v>1</v>
+      </c>
+      <c r="M45" s="14">
+        <v>1</v>
+      </c>
+      <c r="N45" s="47" t="s">
+        <v>300</v>
+      </c>
+      <c r="O45" s="15">
+        <v>3.97</v>
+      </c>
+      <c r="P45" s="15">
+        <f t="shared" ref="P45:P48" si="2">O45*M45</f>
+        <v>3.97</v>
+      </c>
+      <c r="Q45" s="14"/>
+    </row>
+    <row r="46" spans="1:17" s="46" customFormat="1" ht="48">
+      <c r="A46" s="45"/>
+      <c r="B46" s="17">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="I46" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J46" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="K46" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L46" s="14">
+        <v>1</v>
+      </c>
+      <c r="M46" s="14">
+        <v>1</v>
+      </c>
+      <c r="N46" s="47" t="s">
+        <v>300</v>
+      </c>
+      <c r="O46" s="15">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="P46" s="15">
+        <f t="shared" si="2"/>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="Q46" s="14"/>
+    </row>
+    <row r="47" spans="1:17" s="46" customFormat="1" ht="48">
+      <c r="A47" s="45"/>
+      <c r="B47" s="17">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="I47" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="K47" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L47" s="14">
+        <v>1</v>
+      </c>
+      <c r="M47" s="14">
+        <v>1</v>
+      </c>
+      <c r="N47" s="47" t="s">
+        <v>300</v>
+      </c>
+      <c r="O47" s="15">
+        <v>8.59</v>
+      </c>
+      <c r="P47" s="15">
+        <f t="shared" si="2"/>
+        <v>8.59</v>
+      </c>
+      <c r="Q47" s="14"/>
+    </row>
+    <row r="48" spans="1:17" ht="36.75" thickBot="1">
+      <c r="A48" s="1"/>
+      <c r="B48" s="17">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="G48" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="I48" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J48" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="K48" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L48" s="14">
+        <v>1</v>
+      </c>
+      <c r="M48" s="14">
+        <v>1</v>
+      </c>
+      <c r="N48" s="47" t="s">
+        <v>300</v>
+      </c>
+      <c r="O48" s="15">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="P48" s="15">
+        <f t="shared" si="2"/>
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="Q48" s="14"/>
+    </row>
+    <row r="49" spans="1:17" ht="19.5" thickBot="1">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="15">
-        <f>O33*M33</f>
-        <v>3</v>
-      </c>
-      <c r="Q33" s="14"/>
-    </row>
-    <row r="34" spans="1:17" ht="19.5" thickBot="1">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="53" t="s">
-        <v>3</v>
-      </c>
-      <c r="N34" s="54"/>
-      <c r="O34" s="54"/>
-      <c r="P34" s="18">
-        <f>SUM(P8:P33)</f>
-        <v>28.857500000000002</v>
-      </c>
-      <c r="Q34" s="1"/>
+      <c r="O49" s="58"/>
+      <c r="P49" s="18">
+        <f>SUM(P8:P48)</f>
+        <v>34.505699999999997</v>
+      </c>
+      <c r="Q49" s="1"/>
+    </row>
+    <row r="50" spans="1:17">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="M62" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="N49:O49"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="N30" r:id="rId1"/>
-    <hyperlink ref="N29" r:id="rId2"/>
-    <hyperlink ref="N28" r:id="rId3"/>
-    <hyperlink ref="N27" r:id="rId4" display="LCSC"/>
-    <hyperlink ref="N26" r:id="rId5"/>
-    <hyperlink ref="N25" r:id="rId6"/>
-    <hyperlink ref="N24" r:id="rId7"/>
-    <hyperlink ref="N23" r:id="rId8"/>
-    <hyperlink ref="N21" r:id="rId9"/>
-    <hyperlink ref="N20" r:id="rId10"/>
-    <hyperlink ref="N19" r:id="rId11"/>
-    <hyperlink ref="N18" r:id="rId12"/>
-    <hyperlink ref="N17" r:id="rId13"/>
-    <hyperlink ref="N16" r:id="rId14"/>
-    <hyperlink ref="N15" r:id="rId15"/>
-    <hyperlink ref="N14" r:id="rId16"/>
-    <hyperlink ref="N13" r:id="rId17"/>
-    <hyperlink ref="N12" r:id="rId18"/>
-    <hyperlink ref="N11" r:id="rId19"/>
-    <hyperlink ref="N10" r:id="rId20"/>
-    <hyperlink ref="N8" r:id="rId21"/>
-    <hyperlink ref="N31" r:id="rId22"/>
-    <hyperlink ref="N32" r:id="rId23"/>
-    <hyperlink ref="N33" r:id="rId24"/>
-    <hyperlink ref="N9" r:id="rId25"/>
+    <hyperlink ref="N8" r:id="rId1"/>
+    <hyperlink ref="N9" r:id="rId2"/>
+    <hyperlink ref="N10" r:id="rId3"/>
+    <hyperlink ref="N11" r:id="rId4"/>
+    <hyperlink ref="N12" r:id="rId5"/>
+    <hyperlink ref="N13" r:id="rId6"/>
+    <hyperlink ref="N14" r:id="rId7"/>
+    <hyperlink ref="N15" r:id="rId8"/>
+    <hyperlink ref="N16" r:id="rId9"/>
+    <hyperlink ref="N17" r:id="rId10"/>
+    <hyperlink ref="N18" r:id="rId11"/>
+    <hyperlink ref="N19" r:id="rId12"/>
+    <hyperlink ref="N20" r:id="rId13"/>
+    <hyperlink ref="N21" r:id="rId14"/>
+    <hyperlink ref="N22" r:id="rId15"/>
+    <hyperlink ref="N23" r:id="rId16"/>
+    <hyperlink ref="N24" r:id="rId17"/>
+    <hyperlink ref="N25" r:id="rId18"/>
+    <hyperlink ref="N26" r:id="rId19"/>
+    <hyperlink ref="N27" r:id="rId20"/>
+    <hyperlink ref="N28" r:id="rId21"/>
+    <hyperlink ref="N29" r:id="rId22"/>
+    <hyperlink ref="N30" r:id="rId23"/>
+    <hyperlink ref="N31" r:id="rId24"/>
+    <hyperlink ref="N32" r:id="rId25" display="LCSC"/>
+    <hyperlink ref="N33" r:id="rId26"/>
+    <hyperlink ref="N34" r:id="rId27"/>
+    <hyperlink ref="N35" r:id="rId28"/>
+    <hyperlink ref="N36" r:id="rId29"/>
+    <hyperlink ref="N37" r:id="rId30"/>
+    <hyperlink ref="N38" r:id="rId31"/>
+    <hyperlink ref="N39" r:id="rId32"/>
+    <hyperlink ref="N40" r:id="rId33"/>
+    <hyperlink ref="N41" r:id="rId34"/>
+    <hyperlink ref="N42" r:id="rId35"/>
+    <hyperlink ref="N43" r:id="rId36"/>
+    <hyperlink ref="N44" r:id="rId37"/>
+    <hyperlink ref="N45" r:id="rId38"/>
+    <hyperlink ref="N46" r:id="rId39"/>
+    <hyperlink ref="N47" r:id="rId40"/>
+    <hyperlink ref="N48" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId26"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId42"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="18" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" customWidth="1"/>
-    <col min="5" max="5" width="30.85546875" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.140625" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" customWidth="1"/>
     <col min="9" max="9" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.42578125" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" customWidth="1"/>
     <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" thickBot="1">
@@ -3292,14 +4198,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1">
       <c r="A2" s="1"/>
@@ -3310,7 +4216,7 @@
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="40" t="s">
-        <v>156</v>
+        <v>239</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="3"/>
@@ -3334,7 +4240,7 @@
       </c>
       <c r="E3" s="27"/>
       <c r="F3" s="41" t="s">
-        <v>157</v>
+        <v>240</v>
       </c>
       <c r="G3" s="29"/>
       <c r="H3" s="30"/>
@@ -3349,7 +4255,7 @@
       <c r="Q3" s="24"/>
       <c r="R3" s="24"/>
     </row>
-    <row r="4" spans="1:18" ht="15" customHeight="1">
+    <row r="4" spans="1:18">
       <c r="A4" s="1"/>
       <c r="B4" s="8"/>
       <c r="C4" s="26"/>
@@ -3369,7 +4275,7 @@
       <c r="Q4" s="24"/>
       <c r="R4" s="24"/>
     </row>
-    <row r="5" spans="1:18" ht="15" customHeight="1">
+    <row r="5" spans="1:18">
       <c r="A5" s="1"/>
       <c r="B5" s="9"/>
       <c r="C5" s="33"/>
@@ -3389,7 +4295,7 @@
       <c r="Q5" s="35"/>
       <c r="R5" s="35"/>
     </row>
-    <row r="6" spans="1:18" ht="15.75" customHeight="1" thickBot="1">
+    <row r="6" spans="1:18" ht="15.75" thickBot="1">
       <c r="A6" s="1"/>
       <c r="B6" s="11"/>
       <c r="C6" s="36"/>
@@ -3418,53 +4324,53 @@
         <v>5</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>158</v>
+        <v>241</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>159</v>
+        <v>242</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>162</v>
+        <v>253</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>163</v>
+        <v>254</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>160</v>
+        <v>244</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>164</v>
+        <v>255</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>165</v>
+        <v>256</v>
       </c>
       <c r="R7" s="12" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="1"/>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="46" customFormat="1" ht="48">
+      <c r="A8" s="45"/>
       <c r="B8" s="16">
         <f>ROW(B8) - ROW($B$7)</f>
         <v>1</v>
@@ -3473,108 +4379,108 @@
         <v>6</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>71</v>
+        <v>248</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I8" s="50" t="s">
-        <v>199</v>
+        <v>156</v>
+      </c>
+      <c r="I8" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>145</v>
+        <v>219</v>
       </c>
       <c r="L8" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" s="14">
         <f>L8*3</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N8" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="O8" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="P8" s="21" t="s">
-        <v>175</v>
+        <v>258</v>
+      </c>
+      <c r="O8" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P8" s="15" t="s">
+        <v>263</v>
       </c>
       <c r="Q8" s="15">
         <f>P8*N8</f>
-        <v>0.43</v>
+        <v>0.75800000000000001</v>
       </c>
       <c r="R8" s="14"/>
     </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="1"/>
+    <row r="9" spans="1:18" s="46" customFormat="1" ht="36">
+      <c r="A9" s="45"/>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B29" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B43" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>198</v>
+        <v>63</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>101</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="I9" s="50" t="s">
-        <v>199</v>
+        <v>157</v>
+      </c>
+      <c r="I9" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>125</v>
+        <v>183</v>
       </c>
       <c r="K9" s="20" t="s">
-        <v>145</v>
+        <v>220</v>
       </c>
       <c r="L9" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="14">
-        <f t="shared" ref="M9:M33" si="1">L9*3</f>
-        <v>3</v>
-      </c>
-      <c r="N9" s="14">
-        <v>4</v>
-      </c>
-      <c r="O9" s="46" t="s">
-        <v>174</v>
+        <f t="shared" ref="M9:M48" si="1">L9*3</f>
+        <v>6</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="O9" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="P9" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q9" s="21">
-        <f t="shared" ref="Q9" si="2">P9*N9</f>
-        <v>2.5695999999999999</v>
+        <v>264</v>
+      </c>
+      <c r="Q9" s="15">
+        <f t="shared" ref="Q9:Q48" si="2">P9*N9</f>
+        <v>0.38999999999999996</v>
       </c>
       <c r="R9" s="20"/>
     </row>
-    <row r="10" spans="1:18" ht="36">
-      <c r="A10" s="1"/>
+    <row r="10" spans="1:18" s="46" customFormat="1" ht="48">
+      <c r="A10" s="45"/>
       <c r="B10" s="16">
         <f>ROW(B10) - ROW($B$7)</f>
         <v>3</v>
@@ -3583,28 +4489,28 @@
         <v>6</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="I10" s="50" t="s">
-        <v>199</v>
+        <v>156</v>
+      </c>
+      <c r="I10" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>126</v>
+        <v>184</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>146</v>
+        <v>221</v>
       </c>
       <c r="L10" s="14">
         <v>1</v>
@@ -3614,52 +4520,52 @@
         <v>3</v>
       </c>
       <c r="N10" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="O10" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="P10" s="21" t="s">
-        <v>177</v>
+        <v>258</v>
+      </c>
+      <c r="O10" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P10" s="15" t="s">
+        <v>265</v>
       </c>
       <c r="Q10" s="15">
-        <f>P10*N10</f>
-        <v>0.8125</v>
+        <f t="shared" si="2"/>
+        <v>0.43999999999999995</v>
       </c>
       <c r="R10" s="14"/>
     </row>
-    <row r="11" spans="1:18" ht="36">
-      <c r="A11" s="1"/>
+    <row r="11" spans="1:18" s="46" customFormat="1">
+      <c r="A11" s="45"/>
       <c r="B11" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>198</v>
+        <v>65</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>103</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="I11" s="50" t="s">
-        <v>199</v>
+        <v>158</v>
+      </c>
+      <c r="I11" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>127</v>
+        <v>185</v>
       </c>
       <c r="K11" s="20" t="s">
-        <v>147</v>
+        <v>222</v>
       </c>
       <c r="L11" s="20">
         <v>1</v>
@@ -3669,52 +4575,52 @@
         <v>3</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="O11" s="48" t="s">
-        <v>174</v>
+        <v>260</v>
+      </c>
+      <c r="O11" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q11" s="21">
-        <f t="shared" ref="Q11" si="3">P11*N11</f>
-        <v>0.34099999999999997</v>
+        <v>266</v>
+      </c>
+      <c r="Q11" s="15">
+        <f t="shared" si="2"/>
+        <v>0.85499999999999998</v>
       </c>
       <c r="R11" s="20"/>
     </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="1"/>
+    <row r="12" spans="1:18" s="46" customFormat="1" ht="24">
+      <c r="A12" s="45"/>
       <c r="B12" s="16">
         <f>ROW(B12) - ROW($B$7)</f>
         <v>5</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>75</v>
+        <v>248</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="I12" s="50" t="s">
-        <v>199</v>
+        <v>159</v>
+      </c>
+      <c r="I12" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>128</v>
+        <v>186</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>146</v>
+        <v>223</v>
       </c>
       <c r="L12" s="14">
         <v>1</v>
@@ -3723,53 +4629,53 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="N12" s="14">
-        <v>4</v>
-      </c>
-      <c r="O12" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="P12" s="21" t="s">
-        <v>179</v>
+      <c r="N12" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="O12" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P12" s="15" t="s">
+        <v>267</v>
       </c>
       <c r="Q12" s="15">
-        <f>P12*N12</f>
-        <v>1.8264</v>
+        <f t="shared" si="2"/>
+        <v>0.52600000000000002</v>
       </c>
       <c r="R12" s="14"/>
     </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="1"/>
+    <row r="13" spans="1:18" s="46" customFormat="1">
+      <c r="A13" s="45"/>
       <c r="B13" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>196</v>
+        <v>132</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="I13" s="50" t="s">
-        <v>199</v>
+        <v>160</v>
+      </c>
+      <c r="I13" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>129</v>
+        <v>187</v>
       </c>
       <c r="K13" s="20" t="s">
-        <v>148</v>
+        <v>224</v>
       </c>
       <c r="L13" s="20">
         <v>1</v>
@@ -3778,53 +4684,53 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="N13" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="O13" s="46" t="s">
-        <v>174</v>
+      <c r="N13" s="14">
+        <v>4</v>
+      </c>
+      <c r="O13" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="P13" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q13" s="21">
-        <f t="shared" ref="Q13" si="4">P13*N13</f>
-        <v>0.626</v>
+        <v>268</v>
+      </c>
+      <c r="Q13" s="15">
+        <f t="shared" si="2"/>
+        <v>1.7844</v>
       </c>
       <c r="R13" s="20"/>
     </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="1"/>
+    <row r="14" spans="1:18" s="46" customFormat="1">
+      <c r="A14" s="45"/>
       <c r="B14" s="16">
         <f>ROW(B14) - ROW($B$7)</f>
         <v>7</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="I14" s="50" t="s">
-        <v>199</v>
+        <v>101</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="I14" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>166</v>
+        <v>225</v>
       </c>
       <c r="L14" s="14">
         <v>1</v>
@@ -3834,52 +4740,52 @@
         <v>3</v>
       </c>
       <c r="N14" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="O14" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="P14" s="21" t="s">
-        <v>181</v>
+        <v>261</v>
+      </c>
+      <c r="O14" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P14" s="15" t="s">
+        <v>269</v>
       </c>
       <c r="Q14" s="15">
-        <f>P14*N14</f>
-        <v>0.59399999999999997</v>
+        <f t="shared" si="2"/>
+        <v>0.626</v>
       </c>
       <c r="R14" s="14"/>
     </row>
-    <row r="15" spans="1:18" ht="36">
-      <c r="A15" s="1"/>
+    <row r="15" spans="1:18" s="46" customFormat="1" ht="36">
+      <c r="A15" s="45"/>
       <c r="B15" s="17">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>77</v>
+        <v>69</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>248</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="I15" s="50" t="s">
-        <v>199</v>
+        <v>159</v>
+      </c>
+      <c r="I15" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="K15" s="14" t="s">
-        <v>166</v>
+        <v>189</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>226</v>
       </c>
       <c r="L15" s="20">
         <v>1</v>
@@ -3889,107 +4795,107 @@
         <v>3</v>
       </c>
       <c r="N15" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="O15" s="48" t="s">
-        <v>174</v>
+        <v>261</v>
+      </c>
+      <c r="O15" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="P15" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q15" s="21">
-        <f t="shared" ref="Q15" si="5">P15*N15</f>
-        <v>0.55800000000000005</v>
+        <v>270</v>
+      </c>
+      <c r="Q15" s="15">
+        <f t="shared" si="2"/>
+        <v>0.65199999999999991</v>
       </c>
       <c r="R15" s="20"/>
     </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="1"/>
+    <row r="16" spans="1:18" s="46" customFormat="1">
+      <c r="A16" s="45"/>
       <c r="B16" s="16">
         <f>ROW(B16) - ROW($B$7)</f>
         <v>9</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="G16" s="14">
-        <v>1715721</v>
+        <v>107</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>133</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="I16" s="50" t="s">
-        <v>199</v>
+        <v>161</v>
+      </c>
+      <c r="I16" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="L16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" s="14">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="N16" s="14">
-        <v>4</v>
-      </c>
-      <c r="O16" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="P16" s="21" t="s">
-        <v>183</v>
+        <v>6</v>
+      </c>
+      <c r="N16" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="O16" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P16" s="15" t="s">
+        <v>271</v>
       </c>
       <c r="Q16" s="15">
-        <f>P16*N16</f>
-        <v>1.4236</v>
+        <f t="shared" si="2"/>
+        <v>0.59399999999999997</v>
       </c>
       <c r="R16" s="14"/>
     </row>
-    <row r="17" spans="1:18" ht="36">
-      <c r="A17" s="1"/>
+    <row r="17" spans="1:18" s="46" customFormat="1" ht="24">
+      <c r="A17" s="45"/>
       <c r="B17" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>198</v>
+        <v>71</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>108</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="I17" s="50" t="s">
-        <v>199</v>
+        <v>162</v>
+      </c>
+      <c r="I17" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="L17" s="20">
         <v>1</v>
@@ -3999,52 +4905,52 @@
         <v>3</v>
       </c>
       <c r="N17" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="O17" s="48" t="s">
-        <v>174</v>
+        <v>258</v>
+      </c>
+      <c r="O17" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="P17" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q17" s="21">
-        <f t="shared" ref="Q17" si="6">P17*N17</f>
-        <v>0.67500000000000004</v>
+        <v>272</v>
+      </c>
+      <c r="Q17" s="15">
+        <f t="shared" si="2"/>
+        <v>0.34349999999999997</v>
       </c>
       <c r="R17" s="20"/>
     </row>
-    <row r="18" spans="1:18" ht="36">
-      <c r="A18" s="1"/>
+    <row r="18" spans="1:18" s="46" customFormat="1">
+      <c r="A18" s="45"/>
       <c r="B18" s="16">
         <f>ROW(B18) - ROW($B$7)</f>
         <v>11</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>79</v>
+        <v>248</v>
+      </c>
+      <c r="G18" s="14">
+        <v>1715721</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="I18" s="50" t="s">
-        <v>199</v>
+        <v>163</v>
+      </c>
+      <c r="I18" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="L18" s="14">
         <v>1</v>
@@ -4053,53 +4959,53 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="N18" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="O18" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="P18" s="21" t="s">
-        <v>185</v>
+      <c r="N18" s="14">
+        <v>4</v>
+      </c>
+      <c r="O18" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P18" s="15" t="s">
+        <v>273</v>
       </c>
       <c r="Q18" s="15">
-        <f>P18*N18</f>
-        <v>0.48</v>
+        <f t="shared" si="2"/>
+        <v>1.4236</v>
       </c>
       <c r="R18" s="14"/>
     </row>
-    <row r="19" spans="1:18" ht="36">
-      <c r="A19" s="1"/>
+    <row r="19" spans="1:18" s="46" customFormat="1" ht="48">
+      <c r="A19" s="45"/>
       <c r="B19" s="17">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="I19" s="50" t="s">
-        <v>199</v>
+        <v>164</v>
+      </c>
+      <c r="I19" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="L19" s="20">
         <v>1</v>
@@ -4109,52 +5015,52 @@
         <v>3</v>
       </c>
       <c r="N19" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="O19" s="48" t="s">
-        <v>174</v>
+        <v>260</v>
+      </c>
+      <c r="O19" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="P19" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q19" s="21">
-        <f t="shared" ref="Q19" si="7">P19*N19</f>
+        <v>274</v>
+      </c>
+      <c r="Q19" s="15">
+        <f t="shared" si="2"/>
         <v>0.71499999999999997</v>
       </c>
       <c r="R19" s="20"/>
     </row>
-    <row r="20" spans="1:18">
-      <c r="A20" s="1"/>
+    <row r="20" spans="1:18" s="46" customFormat="1" ht="48">
+      <c r="A20" s="45"/>
       <c r="B20" s="16">
         <f>ROW(B20) - ROW($B$7)</f>
         <v>13</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="I20" s="50" t="s">
-        <v>199</v>
+        <v>165</v>
+      </c>
+      <c r="I20" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>149</v>
+        <v>249</v>
       </c>
       <c r="L20" s="14">
         <v>1</v>
@@ -4164,163 +5070,163 @@
         <v>3</v>
       </c>
       <c r="N20" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="O20" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="P20" s="21" t="s">
-        <v>187</v>
+        <v>258</v>
+      </c>
+      <c r="O20" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P20" s="15" t="s">
+        <v>275</v>
       </c>
       <c r="Q20" s="15">
-        <f>P20*N20</f>
-        <v>0.54100000000000004</v>
+        <f t="shared" si="2"/>
+        <v>0.67500000000000004</v>
       </c>
       <c r="R20" s="14"/>
     </row>
-    <row r="21" spans="1:18" ht="24">
-      <c r="A21" s="1"/>
+    <row r="21" spans="1:18" s="46" customFormat="1" ht="48">
+      <c r="A21" s="45"/>
       <c r="B21" s="17">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="H21" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="I21" s="50" t="s">
-        <v>199</v>
-      </c>
-      <c r="J21" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="K21" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="59" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="59" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="G21" s="59" t="s">
+        <v>111</v>
+      </c>
+      <c r="H21" s="59" t="s">
         <v>166</v>
       </c>
-      <c r="L21" s="20">
-        <v>1</v>
-      </c>
-      <c r="M21" s="14">
+      <c r="I21" s="62" t="s">
+        <v>297</v>
+      </c>
+      <c r="J21" s="59" t="s">
+        <v>195</v>
+      </c>
+      <c r="K21" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="L21" s="59">
+        <v>1</v>
+      </c>
+      <c r="M21" s="42">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="N21" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="O21" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="P21" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q21" s="21">
-        <f t="shared" ref="Q21" si="8">P21*N21</f>
-        <v>0.50600000000000001</v>
-      </c>
-      <c r="R21" s="20"/>
-    </row>
-    <row r="22" spans="1:18">
-      <c r="A22" s="1"/>
+      <c r="N21" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="O21" s="66" t="s">
+        <v>257</v>
+      </c>
+      <c r="P21" s="61" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q21" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="R21" s="63" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" s="46" customFormat="1" ht="24">
+      <c r="A22" s="45"/>
       <c r="B22" s="16">
         <f>ROW(B22) - ROW($B$7)</f>
         <v>15</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="F22" s="47" t="s">
-        <v>198</v>
-      </c>
-      <c r="G22" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="H22" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="I22" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="J22" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="K22" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="L22" s="47">
-        <v>2</v>
-      </c>
-      <c r="M22" s="47">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="N22" s="47">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="I22" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="L22" s="14">
+        <v>1</v>
+      </c>
+      <c r="M22" s="14">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N22" s="14" t="s">
+        <v>258</v>
       </c>
       <c r="O22" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="P22" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q22" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="R22" s="45" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18">
-      <c r="A23" s="1"/>
+        <v>257</v>
+      </c>
+      <c r="P22" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q22" s="15">
+        <f t="shared" si="2"/>
+        <v>0.73150000000000004</v>
+      </c>
+      <c r="R22" s="14"/>
+    </row>
+    <row r="23" spans="1:18" s="46" customFormat="1" ht="24">
+      <c r="A23" s="45"/>
       <c r="B23" s="17">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>83</v>
+        <v>77</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>248</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="I23" s="50" t="s">
-        <v>199</v>
+        <v>168</v>
+      </c>
+      <c r="I23" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="K23" s="20" t="s">
-        <v>166</v>
+        <v>228</v>
       </c>
       <c r="L23" s="20">
         <v>1</v>
@@ -4330,52 +5236,52 @@
         <v>3</v>
       </c>
       <c r="N23" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="O23" s="48" t="s">
-        <v>174</v>
+        <v>258</v>
+      </c>
+      <c r="O23" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="P23" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q23" s="21">
-        <f t="shared" ref="Q23" si="9">P23*N23</f>
-        <v>1.1870000000000001</v>
+        <v>277</v>
+      </c>
+      <c r="Q23" s="15">
+        <f t="shared" si="2"/>
+        <v>0.42500000000000004</v>
       </c>
       <c r="R23" s="20"/>
     </row>
-    <row r="24" spans="1:18">
-      <c r="A24" s="1"/>
+    <row r="24" spans="1:18" s="46" customFormat="1" ht="24">
+      <c r="A24" s="45"/>
       <c r="B24" s="16">
         <f>ROW(B24) - ROW($B$7)</f>
         <v>17</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="50" t="s">
-        <v>199</v>
+        <v>169</v>
+      </c>
+      <c r="I24" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>138</v>
+        <v>198</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>150</v>
+        <v>249</v>
       </c>
       <c r="L24" s="14">
         <v>1</v>
@@ -4385,52 +5291,52 @@
         <v>3</v>
       </c>
       <c r="N24" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="O24" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="P24" s="21" t="s">
-        <v>190</v>
+        <v>261</v>
+      </c>
+      <c r="O24" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P24" s="15" t="s">
+        <v>278</v>
       </c>
       <c r="Q24" s="15">
-        <f>P24*N24</f>
-        <v>0.18</v>
+        <f t="shared" si="2"/>
+        <v>0.498</v>
       </c>
       <c r="R24" s="14"/>
     </row>
-    <row r="25" spans="1:18">
-      <c r="A25" s="1"/>
+    <row r="25" spans="1:18" s="46" customFormat="1" ht="36">
+      <c r="A25" s="45"/>
       <c r="B25" s="17">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="I25" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="I25" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J25" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="J25" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="K25" s="20" t="s">
-        <v>151</v>
+      <c r="K25" s="14" t="s">
+        <v>249</v>
       </c>
       <c r="L25" s="20">
         <v>1</v>
@@ -4440,163 +5346,162 @@
         <v>3</v>
       </c>
       <c r="N25" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="O25" s="48" t="s">
-        <v>174</v>
+        <v>262</v>
+      </c>
+      <c r="O25" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q25" s="21">
-        <f t="shared" ref="Q25" si="10">P25*N25</f>
-        <v>0.44</v>
+        <v>279</v>
+      </c>
+      <c r="Q25" s="15">
+        <f t="shared" si="2"/>
+        <v>0.45300000000000001</v>
       </c>
       <c r="R25" s="20"/>
     </row>
-    <row r="26" spans="1:18">
-      <c r="A26" s="1"/>
+    <row r="26" spans="1:18" s="46" customFormat="1">
+      <c r="A26" s="45"/>
       <c r="B26" s="16">
         <f>ROW(B26) - ROW($B$7)</f>
         <v>19</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="I26" s="50" t="s">
-        <v>199</v>
+        <v>171</v>
+      </c>
+      <c r="I26" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>152</v>
+        <v>249</v>
       </c>
       <c r="L26" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="14">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N26" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="O26" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="P26" s="21" t="s">
-        <v>192</v>
+        <v>262</v>
+      </c>
+      <c r="O26" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P26" s="15" t="s">
+        <v>280</v>
       </c>
       <c r="Q26" s="15">
-        <f>P26*N26</f>
-        <v>0.31</v>
+        <f t="shared" si="2"/>
+        <v>0.496</v>
       </c>
       <c r="R26" s="14"/>
     </row>
-    <row r="27" spans="1:18" ht="36">
-      <c r="A27" s="1"/>
+    <row r="27" spans="1:18" s="46" customFormat="1" ht="36">
+      <c r="A27" s="45"/>
       <c r="B27" s="17">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" s="47" t="s">
-        <v>198</v>
-      </c>
-      <c r="G27" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="H27" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="I27" s="50" t="s">
-        <v>199</v>
-      </c>
-      <c r="J27" s="42" t="s">
-        <v>141</v>
-      </c>
-      <c r="K27" s="42" t="s">
-        <v>153</v>
-      </c>
-      <c r="L27" s="42">
-        <v>1</v>
-      </c>
-      <c r="M27" s="43">
+        <v>18</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="I27" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="L27" s="20">
+        <v>1</v>
+      </c>
+      <c r="M27" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="N27" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="O27" s="49" t="s">
-        <v>166</v>
-      </c>
-      <c r="P27" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q27" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="R27" s="45" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18">
-      <c r="A28" s="1"/>
+      <c r="N27" s="14">
+        <v>4</v>
+      </c>
+      <c r="O27" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P27" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q27" s="15">
+        <f t="shared" si="2"/>
+        <v>1.1504000000000001</v>
+      </c>
+      <c r="R27" s="20"/>
+    </row>
+    <row r="28" spans="1:18" s="46" customFormat="1" ht="24">
+      <c r="A28" s="45"/>
       <c r="B28" s="16">
         <f>ROW(B28) - ROW($B$7)</f>
         <v>21</v>
       </c>
-      <c r="C28" s="23" t="s">
-        <v>18</v>
+      <c r="C28" s="22" t="s">
+        <v>16</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I28" s="50" t="s">
-        <v>199</v>
+        <v>173</v>
+      </c>
+      <c r="I28" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>154</v>
+        <v>249</v>
       </c>
       <c r="L28" s="14">
         <v>1</v>
@@ -4606,52 +5511,52 @@
         <v>3</v>
       </c>
       <c r="N28" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="O28" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="P28" s="21" t="s">
-        <v>193</v>
+        <v>258</v>
+      </c>
+      <c r="O28" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P28" s="15" t="s">
+        <v>282</v>
       </c>
       <c r="Q28" s="15">
-        <f>P28*N28</f>
-        <v>0.12</v>
+        <f t="shared" si="2"/>
+        <v>0.44850000000000001</v>
       </c>
       <c r="R28" s="14"/>
     </row>
-    <row r="29" spans="1:18">
-      <c r="A29" s="1"/>
+    <row r="29" spans="1:18" s="46" customFormat="1">
+      <c r="A29" s="45"/>
       <c r="B29" s="17">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="I29" s="50" t="s">
-        <v>199</v>
+        <v>158</v>
+      </c>
+      <c r="I29" s="64" t="s">
+        <v>298</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="K29" s="20" t="s">
-        <v>166</v>
+        <v>229</v>
       </c>
       <c r="L29" s="20">
         <v>1</v>
@@ -4661,302 +5566,1121 @@
         <v>3</v>
       </c>
       <c r="N29" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="O29" s="48" t="s">
-        <v>174</v>
+        <v>259</v>
+      </c>
+      <c r="O29" s="47" t="s">
+        <v>257</v>
       </c>
       <c r="P29" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q29" s="21">
-        <f t="shared" ref="Q29" si="11">P29*N29</f>
-        <v>0.57650000000000001</v>
+        <v>283</v>
+      </c>
+      <c r="Q29" s="15">
+        <f t="shared" si="2"/>
+        <v>0.18</v>
       </c>
       <c r="R29" s="20"/>
     </row>
-    <row r="30" spans="1:18">
-      <c r="A30" s="1"/>
+    <row r="30" spans="1:18" s="46" customFormat="1">
+      <c r="A30" s="45"/>
       <c r="B30" s="16">
         <f>ROW(B30) - ROW($B$7)</f>
         <v>23</v>
       </c>
       <c r="C30" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="I30" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="L30" s="14">
+        <v>1</v>
+      </c>
+      <c r="M30" s="14">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N30" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="O30" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P30" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q30" s="15">
+        <f t="shared" si="2"/>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="R30" s="14"/>
+    </row>
+    <row r="31" spans="1:18" s="46" customFormat="1" ht="48">
+      <c r="A31" s="45"/>
+      <c r="B31" s="17">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="I31" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="L31" s="20">
+        <v>1</v>
+      </c>
+      <c r="M31" s="14">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N31" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="O31" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P31" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q31" s="15">
+        <f t="shared" si="2"/>
+        <v>0.62</v>
+      </c>
+      <c r="R31" s="20"/>
+    </row>
+    <row r="32" spans="1:18" s="46" customFormat="1" ht="24">
+      <c r="A32" s="45"/>
+      <c r="B32" s="16">
+        <f>ROW(B32) - ROW($B$7)</f>
+        <v>25</v>
+      </c>
+      <c r="C32" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D30" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="F30" s="14" t="s">
+      <c r="D32" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="F32" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="G32" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="H32" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="I32" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="J32" s="42" t="s">
+        <v>206</v>
+      </c>
+      <c r="K32" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="L32" s="42">
+        <v>2</v>
+      </c>
+      <c r="M32" s="14">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N32" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="O32" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="P32" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q32" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="R32" s="44" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" s="46" customFormat="1">
+      <c r="A33" s="45"/>
+      <c r="B33" s="17">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="H33" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="I33" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="K33" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="L33" s="20">
+        <v>1</v>
+      </c>
+      <c r="M33" s="14">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N33" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="O33" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P33" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q33" s="15">
+        <f t="shared" si="2"/>
+        <v>0.21</v>
+      </c>
+      <c r="R33" s="20"/>
+    </row>
+    <row r="34" spans="1:18" s="46" customFormat="1">
+      <c r="A34" s="45"/>
+      <c r="B34" s="16">
+        <f>ROW(B34) - ROW($B$7)</f>
+        <v>27</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I34" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="L34" s="14">
+        <v>1</v>
+      </c>
+      <c r="M34" s="14">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N34" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="O34" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P34" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q34" s="15">
+        <f t="shared" si="2"/>
+        <v>0.42999999999999994</v>
+      </c>
+      <c r="R34" s="14"/>
+    </row>
+    <row r="35" spans="1:18" s="46" customFormat="1">
+      <c r="A35" s="45"/>
+      <c r="B35" s="17">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="G30" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="I30" s="50" t="s">
-        <v>199</v>
-      </c>
-      <c r="J30" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="K30" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="L30" s="14">
-        <v>1</v>
-      </c>
-      <c r="M30" s="14">
+      <c r="F35" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="G35" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="H35" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="I35" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J35" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="K35" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="L35" s="20">
+        <v>1</v>
+      </c>
+      <c r="M35" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="N30" s="14" t="s">
+      <c r="N35" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="O35" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P35" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q35" s="15">
+        <f t="shared" si="2"/>
+        <v>0.55999999999999994</v>
+      </c>
+      <c r="R35" s="20"/>
+    </row>
+    <row r="36" spans="1:18" s="46" customFormat="1" ht="48">
+      <c r="A36" s="45"/>
+      <c r="B36" s="16">
+        <f>ROW(B36) - ROW($B$7)</f>
+        <v>29</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="I36" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="L36" s="14">
+        <v>1</v>
+      </c>
+      <c r="M36" s="14">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N36" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="O36" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P36" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q36" s="15">
+        <f t="shared" si="2"/>
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="R36" s="14"/>
+    </row>
+    <row r="37" spans="1:18" s="46" customFormat="1">
+      <c r="A37" s="45"/>
+      <c r="B37" s="17">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="I37" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="K37" s="20" t="s">
+        <v>235</v>
+      </c>
+      <c r="L37" s="20">
+        <v>1</v>
+      </c>
+      <c r="M37" s="14">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N37" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="O37" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P37" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q37" s="15">
+        <f t="shared" si="2"/>
+        <v>0.41399999999999998</v>
+      </c>
+      <c r="R37" s="20"/>
+    </row>
+    <row r="38" spans="1:18" s="46" customFormat="1">
+      <c r="A38" s="45"/>
+      <c r="B38" s="16">
+        <f>ROW(B38) - ROW($B$7)</f>
+        <v>31</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I38" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="L38" s="14">
+        <v>1</v>
+      </c>
+      <c r="M38" s="14">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N38" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="O38" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P38" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q38" s="15">
+        <f t="shared" si="2"/>
+        <v>0.11</v>
+      </c>
+      <c r="R38" s="14"/>
+    </row>
+    <row r="39" spans="1:18" s="46" customFormat="1">
+      <c r="A39" s="45"/>
+      <c r="B39" s="17">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="I39" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="K39" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="L39" s="20">
+        <v>2</v>
+      </c>
+      <c r="M39" s="14">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N39" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="O39" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P39" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q39" s="15">
+        <f t="shared" si="2"/>
+        <v>0.11</v>
+      </c>
+      <c r="R39" s="20"/>
+    </row>
+    <row r="40" spans="1:18" s="46" customFormat="1">
+      <c r="A40" s="45"/>
+      <c r="B40" s="16">
+        <f>ROW(B40) - ROW($B$7)</f>
+        <v>33</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I40" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="L40" s="14">
+        <v>1</v>
+      </c>
+      <c r="M40" s="14">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N40" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="O40" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P40" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q40" s="15">
+        <f t="shared" si="2"/>
+        <v>0.504</v>
+      </c>
+      <c r="R40" s="14"/>
+    </row>
+    <row r="41" spans="1:18" s="46" customFormat="1" ht="36">
+      <c r="A41" s="45"/>
+      <c r="B41" s="17">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="G41" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="H41" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="I41" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="K41" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L41" s="20">
+        <v>1</v>
+      </c>
+      <c r="M41" s="14">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N41" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="O41" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P41" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q41" s="15">
+        <f t="shared" si="2"/>
+        <v>0.74350000000000005</v>
+      </c>
+      <c r="R41" s="20"/>
+    </row>
+    <row r="42" spans="1:18" s="46" customFormat="1" ht="24">
+      <c r="A42" s="45"/>
+      <c r="B42" s="16">
+        <f>ROW(B42) - ROW($B$7)</f>
+        <v>35</v>
+      </c>
+      <c r="C42" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="H42" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="I42" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="K42" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L42" s="14">
+        <v>1</v>
+      </c>
+      <c r="M42" s="14">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N42" s="51" t="s">
+        <v>258</v>
+      </c>
+      <c r="O42" s="53" t="s">
+        <v>257</v>
+      </c>
+      <c r="P42" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q42" s="15">
+        <f t="shared" si="2"/>
+        <v>1.2755000000000001</v>
+      </c>
+      <c r="R42" s="14"/>
+    </row>
+    <row r="43" spans="1:18" s="46" customFormat="1" ht="24">
+      <c r="A43" s="45"/>
+      <c r="B43" s="17">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G43" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="H43" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="I43" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J43" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="K43" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L43" s="20">
+        <v>1</v>
+      </c>
+      <c r="M43" s="14">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N43" s="14">
+        <v>4</v>
+      </c>
+      <c r="O43" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P43" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q43" s="15">
+        <f t="shared" si="2"/>
+        <v>1.9076</v>
+      </c>
+      <c r="R43" s="20"/>
+    </row>
+    <row r="44" spans="1:18" s="46" customFormat="1">
+      <c r="A44" s="45"/>
+      <c r="B44" s="16">
+        <f>ROW(B44) - ROW($B$7)</f>
+        <v>37</v>
+      </c>
+      <c r="C44" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="H44" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="O30" s="48" t="s">
-        <v>174</v>
-      </c>
-      <c r="P30" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q30" s="15">
-        <f>P30*N30</f>
-        <v>0.30299999999999999</v>
-      </c>
-      <c r="R30" s="14"/>
-    </row>
-    <row r="31" spans="1:18" ht="48">
-      <c r="A31" s="1"/>
-      <c r="B31" s="16">
-        <f>ROW(B31) - ROW($B$7)</f>
-        <v>24</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="I31" s="50" t="s">
-        <v>166</v>
-      </c>
-      <c r="J31" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="K31" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="L31" s="14">
-        <v>1</v>
-      </c>
-      <c r="M31" s="14">
+      <c r="I44" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J44" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="K44" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L44" s="14">
+        <v>1</v>
+      </c>
+      <c r="M44" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="N31" s="14">
+      <c r="N44" s="14">
+        <v>4</v>
+      </c>
+      <c r="O44" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="P44" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q44" s="15">
+        <f t="shared" si="2"/>
+        <v>1.9084000000000001</v>
+      </c>
+      <c r="R44" s="14"/>
+    </row>
+    <row r="45" spans="1:18" s="46" customFormat="1" ht="36">
+      <c r="A45" s="45"/>
+      <c r="B45" s="16">
+        <f t="shared" ref="B45:B48" si="3">ROW(B45) - ROW($B$7)</f>
+        <v>38</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="I45" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J45" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="K45" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L45" s="14">
+        <v>1</v>
+      </c>
+      <c r="M45" s="14">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="O31" s="48" t="s">
-        <v>203</v>
-      </c>
-      <c r="P31" s="21">
+      <c r="N45" s="14">
+        <v>4</v>
+      </c>
+      <c r="O45" s="47" t="s">
+        <v>300</v>
+      </c>
+      <c r="P45" s="15">
+        <v>3.97</v>
+      </c>
+      <c r="Q45" s="15">
+        <f t="shared" si="2"/>
+        <v>15.88</v>
+      </c>
+      <c r="R45" s="14"/>
+    </row>
+    <row r="46" spans="1:18" s="46" customFormat="1" ht="48">
+      <c r="A46" s="45"/>
+      <c r="B46" s="16">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="I46" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J46" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="K46" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L46" s="14">
+        <v>1</v>
+      </c>
+      <c r="M46" s="14">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="N46" s="14">
+        <v>3</v>
+      </c>
+      <c r="O46" s="47" t="s">
+        <v>300</v>
+      </c>
+      <c r="P46" s="15">
         <v>1.1499999999999999</v>
       </c>
-      <c r="Q31" s="15">
-        <f>P31*M31</f>
+      <c r="Q46" s="15">
+        <f t="shared" si="2"/>
         <v>3.4499999999999997</v>
       </c>
-      <c r="R31" s="15" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="48">
-      <c r="A32" s="1"/>
-      <c r="B32" s="16">
-        <f t="shared" ref="B32:B33" si="12">ROW(B32) - ROW($B$7)</f>
-        <v>25</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="H32" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="I32" s="50" t="s">
-        <v>166</v>
-      </c>
-      <c r="J32" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="K32" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="L32" s="14">
-        <v>1</v>
-      </c>
-      <c r="M32" s="14">
+      <c r="R46" s="14"/>
+    </row>
+    <row r="47" spans="1:18" s="46" customFormat="1" ht="48">
+      <c r="A47" s="45"/>
+      <c r="B47" s="16">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="I47" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J47" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="K47" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L47" s="14">
+        <v>1</v>
+      </c>
+      <c r="M47" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="N32" s="14">
+      <c r="N47" s="14">
         <v>3</v>
       </c>
-      <c r="O32" s="48" t="s">
-        <v>203</v>
-      </c>
-      <c r="P32" s="21">
-        <v>13.58</v>
-      </c>
-      <c r="Q32" s="15">
-        <f t="shared" ref="Q32:Q33" si="13">P32*M32</f>
-        <v>40.74</v>
-      </c>
-      <c r="R32" s="15" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="48.75" thickBot="1">
-      <c r="A33" s="1"/>
-      <c r="B33" s="16">
-        <f t="shared" si="12"/>
-        <v>26</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="E33" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="G33" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="H33" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="I33" s="50" t="s">
-        <v>166</v>
-      </c>
-      <c r="J33" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="K33" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="L33" s="14">
-        <v>1</v>
-      </c>
-      <c r="M33" s="14">
+      <c r="O47" s="47" t="s">
+        <v>300</v>
+      </c>
+      <c r="P47" s="15">
+        <v>8.59</v>
+      </c>
+      <c r="Q47" s="15">
+        <f t="shared" si="2"/>
+        <v>25.77</v>
+      </c>
+      <c r="R47" s="14"/>
+    </row>
+    <row r="48" spans="1:18" s="46" customFormat="1" ht="36.75" thickBot="1">
+      <c r="A48" s="45"/>
+      <c r="B48" s="16">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="G48" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="I48" s="64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J48" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="K48" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="L48" s="14">
+        <v>1</v>
+      </c>
+      <c r="M48" s="14">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="N33" s="14">
+      <c r="N48" s="14">
         <v>3</v>
       </c>
-      <c r="O33" s="48" t="s">
-        <v>203</v>
-      </c>
-      <c r="P33" s="21">
+      <c r="O48" s="47" t="s">
+        <v>300</v>
+      </c>
+      <c r="P48" s="15">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="Q48" s="15">
+        <f t="shared" si="2"/>
+        <v>3.33</v>
+      </c>
+      <c r="R48" s="14"/>
+    </row>
+    <row r="49" spans="1:18" ht="19.5" thickBot="1">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="15">
-        <f t="shared" si="13"/>
-        <v>9</v>
-      </c>
-      <c r="R33" s="15" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" ht="19.5" thickBot="1">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="53" t="s">
-        <v>3</v>
-      </c>
-      <c r="O34" s="54"/>
-      <c r="P34" s="54"/>
-      <c r="Q34" s="18">
-        <f>SUM(Q8:Q33)</f>
-        <v>68.404600000000002</v>
-      </c>
-      <c r="R34" s="1"/>
-    </row>
-    <row r="35" spans="1:18" ht="19.5" thickBot="1">
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="53" t="s">
+      <c r="P49" s="58"/>
+      <c r="Q49" s="18">
+        <f>SUM(Q8:Q48)</f>
+        <v>72.2029</v>
+      </c>
+      <c r="R49" s="1"/>
+    </row>
+    <row r="50" spans="1:18" ht="19.5" thickBot="1">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="O35" s="54"/>
-      <c r="P35" s="54"/>
-      <c r="Q35" s="19">
-        <f>Q34/3</f>
-        <v>22.801533333333335</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18">
-      <c r="M47" s="38"/>
+      <c r="P50" s="58"/>
+      <c r="Q50" s="19">
+        <f>Q49/3</f>
+        <v>24.067633333333333</v>
+      </c>
+      <c r="R50" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="O49:P49"/>
+    <mergeCell ref="O50:P50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O8" r:id="rId1"/>
@@ -4973,19 +6697,34 @@
     <hyperlink ref="O19" r:id="rId12"/>
     <hyperlink ref="O20" r:id="rId13"/>
     <hyperlink ref="O21" r:id="rId14"/>
-    <hyperlink ref="O23" r:id="rId15"/>
-    <hyperlink ref="O24" r:id="rId16"/>
-    <hyperlink ref="O25" r:id="rId17"/>
-    <hyperlink ref="O26" r:id="rId18"/>
-    <hyperlink ref="O27" r:id="rId19" display="LCSC"/>
-    <hyperlink ref="O28" r:id="rId20"/>
-    <hyperlink ref="O29" r:id="rId21"/>
-    <hyperlink ref="O30" r:id="rId22"/>
-    <hyperlink ref="O31" r:id="rId23"/>
-    <hyperlink ref="O32" r:id="rId24"/>
-    <hyperlink ref="O33" r:id="rId25"/>
+    <hyperlink ref="O22" r:id="rId15"/>
+    <hyperlink ref="O23" r:id="rId16"/>
+    <hyperlink ref="O24" r:id="rId17"/>
+    <hyperlink ref="O25" r:id="rId18"/>
+    <hyperlink ref="O26" r:id="rId19"/>
+    <hyperlink ref="O27" r:id="rId20"/>
+    <hyperlink ref="O28" r:id="rId21"/>
+    <hyperlink ref="O29" r:id="rId22"/>
+    <hyperlink ref="O30" r:id="rId23"/>
+    <hyperlink ref="O31" r:id="rId24"/>
+    <hyperlink ref="O32" r:id="rId25" display="LCSC"/>
+    <hyperlink ref="O33" r:id="rId26"/>
+    <hyperlink ref="O34" r:id="rId27"/>
+    <hyperlink ref="O35" r:id="rId28"/>
+    <hyperlink ref="O36" r:id="rId29"/>
+    <hyperlink ref="O37" r:id="rId30"/>
+    <hyperlink ref="O38" r:id="rId31"/>
+    <hyperlink ref="O39" r:id="rId32"/>
+    <hyperlink ref="O40" r:id="rId33"/>
+    <hyperlink ref="O41" r:id="rId34"/>
+    <hyperlink ref="O42" r:id="rId35"/>
+    <hyperlink ref="O43" r:id="rId36"/>
+    <hyperlink ref="O44" r:id="rId37"/>
+    <hyperlink ref="O45" r:id="rId38"/>
+    <hyperlink ref="O46" r:id="rId39"/>
+    <hyperlink ref="O47" r:id="rId40"/>
+    <hyperlink ref="O48" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
 </worksheet>
 </file>